--- a/workspaces/btc_daily_14days/volatility/realized_vol_14.xlsx
+++ b/workspaces/btc_daily_14days/volatility/realized_vol_14.xlsx
@@ -575,46 +575,46 @@
         <v>150</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.160104986876647</v>
+        <v>-1.157130480278092</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.105007717600806</v>
+        <v>-0.1050625200562578</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-3.835003093833727</v>
+        <v>-3.823373809093141</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.039873536643974</v>
+        <v>-5.024362964450361</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.575962085048921</v>
+        <v>-1.571910322572634</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.948466821220606</v>
+        <v>-3.936697392465668</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.031265920564103</v>
+        <v>-2.025649735446997</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.171807039101445</v>
+        <v>0.169954341609639</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.118855772555754</v>
+        <v>4.104155655340961</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.9406399292656</v>
+        <v>5.920000405527318</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.410330027133824</v>
+        <v>8.381644673595133</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.115624859848651</v>
+        <v>9.08453043725504</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>9.36523253835049</v>
+        <v>9.333267392961879</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.949476171109993</v>
+        <v>8.918780915908727</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>221</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.972625028206309</v>
+        <v>4.954475959241144</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.340700748399406</v>
+        <v>8.311141770293538</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.77879859148706</v>
+        <v>4.761501235370361</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.174743090374797</v>
+        <v>7.149137167708595</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.808697658552731</v>
+        <v>9.773389568050092</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.749890103606695</v>
+        <v>8.718480547419475</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.667472086118586</v>
+        <v>8.636280106429474</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.935385611244605</v>
+        <v>5.913217526271211</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.876174144499068</v>
+        <v>5.853870888562639</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.932995955220299</v>
+        <v>5.910325831900224</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.275902998956759</v>
+        <v>5.25530611538094</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.404474939193854</v>
+        <v>4.386735948675607</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.800118379556409</v>
+        <v>5.777419063056968</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.960672370322072</v>
+        <v>6.933863872168153</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>219</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.301082227735229</v>
+        <v>2.290567890731609</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.420878631847181</v>
+        <v>-3.410501960059221</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.187506913584663</v>
+        <v>-5.169990928315237</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.972409083830705</v>
+        <v>-5.952440820858605</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.426916601114364</v>
+        <v>-7.402696451379001</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-5.759270915998357</v>
+        <v>-5.740780703834716</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-5.388142143128199</v>
+        <v>-5.37109018507325</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-6.315120456408266</v>
+        <v>-6.294610088201374</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.750610532167087</v>
+        <v>-7.725144799184186</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.14695200690808</v>
+        <v>-8.120217485852962</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.690846983821245</v>
+        <v>-4.67704331900908</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.657406170061165</v>
+        <v>-4.643743705085839</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.788832746101981</v>
+        <v>-2.78250874962017</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.996671807554733</v>
+        <v>-2.989894883178025</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.766165592937249</v>
+        <v>-3.778067252357125</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.091720826793328</v>
+        <v>-4.105899521186622</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4406817969355643</v>
+        <v>0.4430693118277418</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.752135346035566</v>
+        <v>2.763844536751812</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.149689682220647</v>
+        <v>-2.156141712438533</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.3293698375789234</v>
+        <v>0.3324640883446435</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.245148916452365</v>
+        <v>0.2480735472376949</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.5096400259992677</v>
+        <v>0.5133483900939808</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.542116455307955</v>
+        <v>1.549909761559576</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.425645423344591</v>
+        <v>1.433114049306482</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1276697010832208</v>
+        <v>0.1310429908504105</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.5267890284261441</v>
+        <v>0.531743431532</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4724825650244995</v>
+        <v>0.4781306873451214</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.451142745425969</v>
+        <v>1.460905458033281</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.353382297801012</v>
+        <v>-2.358108153897945</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.64562817967289</v>
+        <v>-5.659290270494274</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-9.681953468902471</v>
+        <v>-9.70541996702805</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-13.04229397071189</v>
+        <v>-13.07338706667593</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-13.14582616427241</v>
+        <v>-13.17757375255277</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-12.29494155075756</v>
+        <v>-12.32412677761127</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-10.70169641929002</v>
+        <v>-10.72683658593427</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-8.926830711709428</v>
+        <v>-8.947681068870573</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-8.42994592948348</v>
+        <v>-8.449300035257679</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.473598018829797</v>
+        <v>-6.488033300436122</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-7.5223080077145</v>
+        <v>-7.538957203052831</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.963338500774128</v>
+        <v>-4.9735348268823</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.980067291669066</v>
+        <v>-3.98720923674508</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.327421566038126</v>
+        <v>-2.330045375171139</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.164490951788927</v>
+        <v>-2.16482983774511</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1576435121216022</v>
+        <v>-0.1577654561790638</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4343298865449654</v>
+        <v>0.4342401785144361</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.55142512441563</v>
+        <v>1.551512744362938</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.999846014606611</v>
+        <v>1.999977961576981</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.6638590576470165</v>
+        <v>-0.6641356045587443</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.882575654141334</v>
+        <v>-1.883022133657875</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.666828062609483</v>
+        <v>-3.667554907234361</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.05904847011184</v>
+        <v>-4.059811958744696</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.250966823714229</v>
+        <v>-4.251716331515041</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.105138343799389</v>
+        <v>-6.106201768668534</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.403246719180878</v>
+        <v>-6.404298542014509</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.496010695284426</v>
+        <v>-6.497009065725067</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.898527623417202</v>
+        <v>-7.899700932276012</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.854387766746633</v>
+        <v>1.862941858036017</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1195046867973346</v>
+        <v>-0.1229896138516224</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.5725831283451228</v>
+        <v>0.5705330938537116</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3405174203728336</v>
+        <v>0.3375048696873506</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.976009248779</v>
+        <v>1.979861287272996</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.11304814561452</v>
+        <v>2.117685556472331</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.115129750221328</v>
+        <v>3.125014688296133</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.664862601107245</v>
+        <v>4.68186692485456</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.879853771547573</v>
+        <v>3.893926590027533</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.759942389666868</v>
+        <v>3.77477077470995</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.558799214077624</v>
+        <v>3.571903928127817</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.229215166356077</v>
+        <v>3.242521643323236</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.9945667715642728</v>
+        <v>0.9994949664529429</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.785206738725634</v>
+        <v>3.8044256847651</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.01975410968366</v>
+        <v>-3.022627873907666</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2809529791064733</v>
+        <v>0.2805070528681384</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.289593044439698</v>
+        <v>1.289821708542227</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.4924345247071</v>
+        <v>-3.497081997639711</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.329101353814437</v>
+        <v>-3.333567332425083</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.277273451186495</v>
+        <v>-1.27959414192182</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.3093755895113262</v>
+        <v>-0.3104447191442077</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.977826976619447</v>
+        <v>0.9782354169392704</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.593485460370189</v>
+        <v>-2.596637223718325</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.796927667892348</v>
+        <v>-3.800999220246737</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.112716506910125</v>
+        <v>-6.119367188883388</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.08076667002409</v>
+        <v>-6.0869991878305</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-7.208082059203555</v>
+        <v>-7.215239210004263</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.464129552155526</v>
+        <v>-7.47089044559354</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.58468667978989</v>
+        <v>2.610222127019668</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.535613066825768</v>
+        <v>2.554396853452886</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.703244360229178</v>
+        <v>3.731813887038427</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.78662249283672</v>
+        <v>5.830224883716049</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.810701277764508</v>
+        <v>6.865689802450206</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.373768215480212</v>
+        <v>4.406430415568188</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.50778449820789</v>
+        <v>3.535820560475621</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.868726099426432</v>
+        <v>1.883154648195728</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.026527899351841</v>
+        <v>1.027495839188319</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.779679523666402</v>
+        <v>-1.806886054929834</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.542155488181223</v>
+        <v>-2.583647984880514</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.849892688118551</v>
+        <v>-3.900710273708036</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.434272385251539</v>
+        <v>-4.490360706222631</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.541036256097314</v>
+        <v>-6.612180875922583</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.67897547289347</v>
+        <v>2.70713026543325</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.993510234313455</v>
+        <v>6.047937604849871</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.613419852840018</v>
+        <v>4.652926751842486</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.728894660324308</v>
+        <v>5.774793246212596</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6.668305957567469</v>
+        <v>6.725497830714048</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>8.936191245036767</v>
+        <v>9.016401033532709</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>7.866235852887691</v>
+        <v>7.939485368854697</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8.876884966421407</v>
+        <v>8.961996355289877</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>11.06291153025851</v>
+        <v>11.16380770899574</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>13.94810706748983</v>
+        <v>14.0756047595595</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>14.24554625593844</v>
+        <v>14.36836387305287</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>13.29132597064421</v>
+        <v>13.40772215477635</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>12.38240591798402</v>
+        <v>12.4899551060205</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>8.191302549828535</v>
+        <v>8.262064497998225</v>
       </c>
     </row>
     <row r="16">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 14.15</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4080~4093</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4080</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.2579142547323272</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 17.87</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3930~3943</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3930</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.2235930247496682</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 21.6</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3709~3722</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3709</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.5321271971578554</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 25.33</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3490~3503</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3490</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.7092533359108018</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 29.05</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3217~3228</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3217</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.4488286547824671</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 32.78</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2862~2871</t>
-        </is>
+      <c r="B11" t="n">
+        <v>2862</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.2120032801542422</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 36.5</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2559~2567</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2559</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.01922237320646047</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 40.23</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2285~2291</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2285</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.2018625890882007</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 43.96</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2001~2006</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2001</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.1984859071080649</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 47.68</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1748~1750</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1748</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.1505811773528265</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 51.41</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1547~1547</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1547</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.521880466299173</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 55.14</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1260~1260</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1260</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.04624421947256963</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 58.86</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1030~1030</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1030</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.06625385419055618</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 62.59</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>909~909</t>
-        </is>
+      <c r="B19" t="n">
+        <v>909</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.4582347998579408</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 66.32</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>797~797</t>
-        </is>
+      <c r="B20" t="n">
+        <v>797</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.301468433133437</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 70.04</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>703~703</t>
-        </is>
+      <c r="B21" t="n">
+        <v>703</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.9998394581900598</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 73.77</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>619~619</t>
-        </is>
+      <c r="B22" t="n">
+        <v>619</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.7971539906461658</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 77.49</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>535~535</t>
-        </is>
+      <c r="B23" t="n">
+        <v>535</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.3439056099295996</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 81.22</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>466~466</t>
-        </is>
+      <c r="B24" t="n">
+        <v>466</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.5621078481069759</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 84.95</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>381~381</t>
-        </is>
+      <c r="B25" t="n">
+        <v>381</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.574803149606296</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 88.67</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>341~341</t>
-        </is>
+      <c r="B26" t="n">
+        <v>341</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-2.053555622262763</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 92.4</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>295~295</t>
-        </is>
+      <c r="B27" t="n">
+        <v>295</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.645980693091332</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 96.13</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>236~236</t>
-        </is>
+      <c r="B28" t="n">
+        <v>236</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-1.22225187953201</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 99.85</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>201~201</t>
-        </is>
+      <c r="B29" t="n">
+        <v>201</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-2.742194539115445</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 103.6</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>172~172</t>
-        </is>
+      <c r="B30" t="n">
+        <v>172</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-3.074833669047187</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 107.3</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>150~150</t>
-        </is>
+      <c r="B31" t="n">
+        <v>150</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-1.826771653543304</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 111</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>131~131</t>
-        </is>
+      <c r="B32" t="n">
+        <v>131</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-1.348400152271047</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 114.8</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>112~112</t>
-        </is>
+      <c r="B33" t="n">
+        <v>112</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-1.600581177352836</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 118.5</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>102~102</t>
-        </is>
+      <c r="B34" t="n">
+        <v>102</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-1.513046163347234</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 122.2</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>1.077990251218594</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 14.15</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>12.98275215598051</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 17.87</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>234~234</t>
-        </is>
+      <c r="B7" t="n">
+        <v>234</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>3.916818090046434</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 21.6</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>455~455</t>
-        </is>
+      <c r="B8" t="n">
+        <v>455</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.429638602866945</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 25.33</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>674~674</t>
-        </is>
+      <c r="B9" t="n">
+        <v>674</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3.738015685724747</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 29.05</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>947~949</t>
-        </is>
+      <c r="B10" t="n">
+        <v>947</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1.563463681897503</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 32.78</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1302~1306</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1302</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.492779137676699</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 36.5</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1605~1610</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1605</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.008966270520531339</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 40.23</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1879~1886</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1879</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.2637196861526974</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 43.96</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2163~2171</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2163</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.1673213234342938</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 47.68</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2416~2427</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2416</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.1229605261023394</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 51.41</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2617~2630</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2617</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.3202498927177828</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 55.14</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2904~2917</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2904</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.008008083665579591</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 58.86</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3134~3147</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3134</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.03277712306933722</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 62.59</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3255~3268</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3255</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.1381406271584424</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 66.32</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3367~3380</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3367</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.3172125673639883</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 70.04</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3461~3474</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3461</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.2123763027030989</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 73.77</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3545~3558</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3545</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.1484953503914852</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 77.49</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3629~3642</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3629</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.0601036896747047</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 81.22</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3698~3711</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3698</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.07999202201583699</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 84.95</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3783~3796</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3783</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.1672571487046639</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 88.67</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3823~3836</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3823</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.1916503137837751</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 92.4</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3869~3882</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3869</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.134073271752932</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 96.13</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3928~3941</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3928</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.08205013449695286</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 99.85</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3963~3976</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3963</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.1474067502125607</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 103.6</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3992~4005</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3992</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.140768920738843</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 107.3</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>4014~4027</t>
-        </is>
+      <c r="B31" t="n">
+        <v>4014</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.07671315731671768</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 111</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4033~4046</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4033</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.05228585181177436</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 114.8</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4052~4065</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4052</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.05268714104463612</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 118.5</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4062~4075</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4062</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.04643898040352923</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 122.2</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4080~4093</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4080</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.01359468473477676</v>

--- a/workspaces/btc_daily_14days/volatility/realized_vol_14.xlsx
+++ b/workspaces/btc_daily_14days/volatility/realized_vol_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Realized VOL-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Realized VOL-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>150</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.157130480278092</v>
+        <v>-1.144651000458666</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1050625200562578</v>
+        <v>-0.09219283723001581</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-3.823373809093141</v>
+        <v>-3.810406129205262</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.024362964450361</v>
+        <v>-5.011420364033185</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.571910322572634</v>
+        <v>-1.558830702457556</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.936697392465668</v>
+        <v>-3.923683271426192</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.025649735446997</v>
+        <v>-2.012607889258561</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.169954341609639</v>
+        <v>0.1831151439995722</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.104155655340961</v>
+        <v>4.117338767566942</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.920000405527318</v>
+        <v>5.933393273100016</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.381644673595133</v>
+        <v>8.395093195620021</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.08453043725504</v>
+        <v>9.097976976670786</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>9.333267392961879</v>
+        <v>9.346820554830416</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.918780915908727</v>
+        <v>8.908351280210873</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>221</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.954475959241144</v>
+        <v>4.966956846828573</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.311141770293538</v>
+        <v>8.324014770583759</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.761501235370361</v>
+        <v>4.77447155967392</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.149137167708595</v>
+        <v>7.162084625921395</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.773389568050092</v>
+        <v>9.786473404289573</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.718480547419475</v>
+        <v>8.731498943892376</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.636280106429474</v>
+        <v>8.649324848601672</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.913217526271211</v>
+        <v>5.926378834465062</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.853870888562639</v>
+        <v>5.867053227374569</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.910325831900224</v>
+        <v>5.923717643013525</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.25530611538094</v>
+        <v>5.268753258234582</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.386735948675607</v>
+        <v>4.400181359946785</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.777419063056968</v>
+        <v>5.790971744489077</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.933863872168153</v>
+        <v>6.923434236470001</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>219</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.290567890731609</v>
+        <v>2.303041400564766</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.410501960059221</v>
+        <v>-3.397644106718339</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.169990928315237</v>
+        <v>-5.15703364015495</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.952440820858605</v>
+        <v>-5.939507358106972</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.402696451379001</v>
+        <v>-7.389627780235791</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-5.740780703834716</v>
+        <v>-5.727774164312386</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-5.37109018507325</v>
+        <v>-5.358055575217392</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-6.294610088201374</v>
+        <v>-6.281456891597664</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.725144799184186</v>
+        <v>-7.711969779808982</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.120217485852962</v>
+        <v>-8.106831700693682</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.67704331900908</v>
+        <v>-4.663599726517809</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.643743705085839</v>
+        <v>-4.630300543191055</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.78250874962017</v>
+        <v>-2.768957131511996</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.989894883178025</v>
+        <v>-3.000324518876177</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>273</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.778067252357125</v>
+        <v>-3.955480816068274</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.105899521186622</v>
+        <v>-4.289991546602174</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4430693118277418</v>
+        <v>0.2578916542509049</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.763844536751812</v>
+        <v>2.776778703009263</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.156141712438533</v>
+        <v>-2.143075711272438</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.3324640883446435</v>
+        <v>0.3454692252423328</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2480735472376949</v>
+        <v>0.2611066853583139</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.5133483900939808</v>
+        <v>0.526500831693312</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.549909761559576</v>
+        <v>1.563085168061079</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.433114049306482</v>
+        <v>1.446500177107033</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1310429908504105</v>
+        <v>0.144485731303476</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.531743431532</v>
+        <v>0.5451860983108006</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4781306873451214</v>
+        <v>0.491681920387073</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.460905458033281</v>
+        <v>1.450475822335129</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>355</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.358108153897945</v>
+        <v>-2.346252977953647</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.659290270494274</v>
+        <v>-5.648309036016215</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-9.70541996702805</v>
+        <v>-9.695725425500001</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-13.07338706667593</v>
+        <v>-13.21603999388083</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-13.17757375255277</v>
+        <v>-13.32219682638843</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-12.32412677761127</v>
+        <v>-12.31114207117478</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-10.72683658593427</v>
+        <v>-10.71381992161208</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-8.947681068870573</v>
+        <v>-8.934541657467427</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-8.449300035257679</v>
+        <v>-8.436135589836894</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.488033300436122</v>
+        <v>-6.47465501263504</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-7.538957203052831</v>
+        <v>-7.525520394663637</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.9735348268823</v>
+        <v>-4.960095551190342</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.98720923674508</v>
+        <v>-3.973659569219627</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.330045375171139</v>
+        <v>-2.340475010869291</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>303</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.16482983774511</v>
+        <v>-2.153070669037646</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1577654561790638</v>
+        <v>-0.145130246554757</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4342401785144361</v>
+        <v>0.4470453007371802</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.551512744362938</v>
+        <v>1.56468919390219</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.999977961576981</v>
+        <v>2.013385890981048</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.6641356045587443</v>
+        <v>-0.6510834877754306</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.883022133657875</v>
+        <v>-2.053304736849327</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.667554907234361</v>
+        <v>-3.654423107740378</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.059811958744696</v>
+        <v>-4.046654336361478</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.251716331515041</v>
+        <v>-4.238344385703698</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.106201768668534</v>
+        <v>-6.092770271492931</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.404298542014509</v>
+        <v>-6.390863333845182</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.497009065725067</v>
+        <v>-6.483461521305777</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.899700932276012</v>
+        <v>-7.910130567974164</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>274</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.862941858036017</v>
+        <v>1.876271027135999</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1229896138516224</v>
+        <v>-0.1104085260346821</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.5705330938537116</v>
+        <v>0.5833468522296883</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3375048696873506</v>
+        <v>0.3501998480429336</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.979861287272996</v>
+        <v>1.993335441827227</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.117685556472331</v>
+        <v>1.928330873878437</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.125014688296133</v>
+        <v>3.139013356440891</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.68186692485456</v>
+        <v>4.492097243813056</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.893926590027533</v>
+        <v>3.907080506286526</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.77477077470995</v>
+        <v>3.788139751111395</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.571903928127817</v>
+        <v>3.585333681222835</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.242521643323236</v>
+        <v>3.25595571160332</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.9994949664529429</v>
+        <v>1.013041552161155</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.8044256847651</v>
+        <v>3.793996049066948</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.022627873907666</v>
+        <v>-3.000208162180037</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2805070528681384</v>
+        <v>0.2949526600396197</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.289821708542227</v>
+        <v>1.302041306621987</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.497081997639711</v>
+        <v>-3.468096670494312</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.333567332425083</v>
+        <v>-3.305075420993617</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.27959414192182</v>
+        <v>-1.25855864293986</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.3104447191442077</v>
+        <v>-0.2936963161428565</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.9782354169392704</v>
+        <v>0.9900097324649693</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.596637223718325</v>
+        <v>-2.571107457401112</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.800999220246737</v>
+        <v>-3.771634180058584</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.119367188883388</v>
+        <v>-6.079795538609261</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.0869991878305</v>
+        <v>-6.049062790335967</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-7.215239210004263</v>
+        <v>-7.173549070771422</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.47089044559354</v>
+        <v>-7.302175035578813</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>253</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.610222127019668</v>
+        <v>2.622744416695291</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.554396853452886</v>
+        <v>2.567306663028937</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.731813887038427</v>
+        <v>3.74482101845603</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.830224883716049</v>
+        <v>5.843204026114513</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.865689802450206</v>
+        <v>6.878800606825145</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.406430415568188</v>
+        <v>4.419473311862554</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.535820560475621</v>
+        <v>3.548886814776097</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.883154648195728</v>
+        <v>1.896335657490965</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.027495839188319</v>
+        <v>1.04094193048477</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.806886054929834</v>
+        <v>-1.791692031189754</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.583647984880514</v>
+        <v>-2.79757144910257</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.900710273708036</v>
+        <v>-4.112893557602966</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.490360706222631</v>
+        <v>-4.703850341462136</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.612180875922583</v>
+        <v>-6.622610511620735</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>201</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.70713026543325</v>
+        <v>2.719652555108873</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.047937604849871</v>
+        <v>6.060847414425922</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.652926751842486</v>
+        <v>4.665933883260088</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.774793246212596</v>
+        <v>5.78777238861106</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6.725497830714048</v>
+        <v>6.738608635088987</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>9.016401033532709</v>
+        <v>9.029443929827075</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>7.939485368854697</v>
+        <v>7.952551623155173</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8.961996355289877</v>
+        <v>8.975177364585115</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>11.16380770899574</v>
+        <v>10.89799051723085</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>14.0756047595595</v>
+        <v>13.80455451968172</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>14.36836387305287</v>
+        <v>14.38182116676309</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>13.40772215477635</v>
+        <v>13.42117444349646</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>12.4899551060205</v>
+        <v>12.5035111523721</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>8.262064497998225</v>
+        <v>8.251634862300072</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>287</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.016086403833633</v>
+        <v>-3.00356411415801</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.295684930937263</v>
+        <v>1.308594740513314</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.946112391588066</v>
+        <v>1.959119523005668</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.727933468446437</v>
+        <v>1.740912610844902</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.8410801976251321</v>
+        <v>0.8541910020000714</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.300502254903066</v>
+        <v>-1.2874593586087</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.082100083673645</v>
+        <v>-2.069033829373168</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.8071232037095015</v>
+        <v>-0.7939421944142637</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.913419257139225</v>
+        <v>-1.900220518184462</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.415112386417981</v>
+        <v>-2.40170725876515</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.226137487739045</v>
+        <v>-1.212680194028827</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4948902188953639</v>
+        <v>-0.4814379301752538</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1301513374071206</v>
+        <v>0.1437073837587235</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.379872669683408</v>
+        <v>0.3694430339852559</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>230</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.5500399406595946</v>
+        <v>0.5625622303352174</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.590640240738814</v>
+        <v>4.603550050314865</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.065336751533529</v>
+        <v>5.078343882951131</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6.934720318923638</v>
+        <v>6.947699461322102</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.222386060373204</v>
+        <v>4.235496864748143</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.345914954610549</v>
+        <v>2.358957850904915</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.826398628642671</v>
+        <v>1.839464882943147</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.793997838556827</v>
+        <v>1.807178847852065</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.602563169765929</v>
+        <v>2.615761908720692</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.056785810824806</v>
+        <v>3.070190938477637</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>4.591162921289936</v>
+        <v>4.604620215000153</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.060328687331015</v>
+        <v>5.073780976051125</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.074856685081677</v>
+        <v>5.08841273143328</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3.585447582575348</v>
+        <v>3.575017946877196</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>121</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.878462506236311</v>
+        <v>2.890984795911933</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.266888893272053</v>
+        <v>1.279798702848105</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.8720201866754635</v>
+        <v>0.8850273180930657</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.956404366667499</v>
+        <v>-3.943425224269035</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.943190947185947</v>
+        <v>2.956301751560886</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>9.025756851843802</v>
+        <v>9.038799748138167</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5.635238010604581</v>
+        <v>5.648304264905057</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.688715768847928</v>
+        <v>2.701896778143166</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.9748233206820629</v>
+        <v>0.9880220596368261</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.5281944263292</v>
+        <v>-1.514789298676369</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.212286593622267</v>
+        <v>-4.198829299912049</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.8721183123098015</v>
+        <v>-0.8586660235896915</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.186965919720649</v>
+        <v>1.200521966072252</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.0895798139805</v>
+        <v>3.079150178282347</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>112</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>5.542275965504317</v>
+        <v>5.554798255179939</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.144988066825711</v>
+        <v>2.157897876401762</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.035594925485114</v>
+        <v>-0.02258779406751188</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.773229635693873</v>
+        <v>2.786208778092337</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.341951277764565</v>
+        <v>1.355062082139504</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.639393215480169</v>
+        <v>1.652436111774534</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6618023553507513</v>
+        <v>0.6748686096512273</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.658904670854916</v>
+        <v>4.672085680150154</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>8.169333356101184</v>
+        <v>8.182532095055947</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>6.42635102821616</v>
+        <v>6.439756155868992</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>8.007311989612973</v>
+        <v>8.02076928332319</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.684552289815443</v>
+        <v>2.698004578535553</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.41427374970079</v>
+        <v>-0.4007177033491871</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.950266703138894</v>
+        <v>-1.960696338837046</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>94</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.557268107444017</v>
+        <v>-3.544745817768394</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.041182145940127</v>
+        <v>-3.028272336364076</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.436050852536781</v>
+        <v>-3.423043721119178</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.305797719929281</v>
+        <v>-3.292818577530817</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-7.035708296703575</v>
+        <v>-7.022597492328636</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.546776997285789</v>
+        <v>-3.533734100991424</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.68763822161214</v>
+        <v>1.700704475912616</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.220454822830639</v>
+        <v>1.233635832125877</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.287114511116485</v>
+        <v>3.300313250071248</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.500819113322606</v>
+        <v>3.514224240975437</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>7.551384937941137</v>
+        <v>7.564842231651355</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>10.77725745698869</v>
+        <v>10.7907097457088</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>13.54849220774592</v>
+        <v>13.56204825409752</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>11.67055396555412</v>
+        <v>11.66012432985597</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>84</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.493438320209911</v>
+        <v>-2.480916030534289</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.295488123650422</v>
+        <v>-5.282578314074371</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-11.64273778262797</v>
+        <v>-11.62973065121037</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-12.70296084049665</v>
+        <v>-12.68998169809819</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-6.098524912711682</v>
+        <v>-6.085414108336742</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.801082974996021</v>
+        <v>-5.788040078701655</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.972047710097421</v>
+        <v>-3.958866700802183</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.033047596279793</v>
+        <v>-4.01984885732503</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.069208171073235</v>
+        <v>1.082613298726066</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.516497534196652</v>
+        <v>-1.503040240486435</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2916381863751027</v>
+        <v>-0.2781858976549927</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-6.664273749700953</v>
+        <v>-6.650717703349351</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.224076226948483</v>
+        <v>-5.234505862646635</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>84</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-3.683914510686236</v>
+        <v>-3.671392221010613</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>6.214405074514822</v>
+        <v>6.227412205932424</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.798198935734753</v>
+        <v>-0.7852197933362888</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1461439603307255</v>
+        <v>-0.1330331559557862</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.50486431131592</v>
+        <v>-3.491798057015444</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4006191386687803</v>
+        <v>-0.3874381293735425</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-6.413999977232173</v>
+        <v>-6.40080123827741</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.3260213437205337</v>
+        <v>-0.312564050010316</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-5.053542948279798</v>
+        <v>-5.040090659559688</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.283321368748574</v>
+        <v>-4.269765322396971</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.033600036472151</v>
+        <v>-4.044029672170304</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>69</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.129750085587162</v>
+        <v>1.142272375262785</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.9674518349417127</v>
+        <v>0.9803616445177639</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.92040921530176</v>
+        <v>4.933416346719362</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>7.949213072546819</v>
+        <v>7.962192214945283</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>7.410791857474649</v>
+        <v>7.423902661849588</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>9.157509157509146</v>
+        <v>9.170552053803512</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6.174224715599202</v>
+        <v>6.187290969899678</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.707041316817609</v>
+        <v>5.720222326112847</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.196766068316641</v>
+        <v>4.209964807271405</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.001185203667944</v>
+        <v>-0.9877800760151132</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.655213890304232</v>
+        <v>-2.641756596594014</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.620830732958851</v>
+        <v>-2.607378444238741</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.591809981584866</v>
+        <v>-1.578253935233263</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.342088649308735</v>
+        <v>-1.352518285006887</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>85</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.977149915084105</v>
+        <v>3.989672204759728</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.869717815527174</v>
+        <v>-5.856808005951123</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-10.97046887506497</v>
+        <v>-10.95746174364737</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.957862801280967</v>
+        <v>-4.944883658882503</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-5.496284016353137</v>
+        <v>-5.483173211978198</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-8.72825384334336</v>
+        <v>-8.715210947048995</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-13.51886991355682</v>
+        <v>-13.50580365925634</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-12.80958272410302</v>
+        <v>-12.79640171480779</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.0705938603028784</v>
+        <v>0.0837925992576416</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.132472501195572</v>
+        <v>-3.119067373542741</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-9.219578766689658</v>
+        <v>-9.20612147297944</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-15.06754855052066</v>
+        <v>-15.05409626180055</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-13.13486198499501</v>
+        <v>-13.1213059386434</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-14.06161124095402</v>
+        <v>-14.07204087665217</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>40</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.506561679790032</v>
+        <v>2.519083969465655</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.8949880668257748</v>
+        <v>0.907897876401826</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.6303724928366847</v>
+        <v>0.6433516352351489</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-7.408048722235492</v>
+        <v>-7.394937917860553</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.19534050179211</v>
+        <v>-2.182274247491634</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.337476099426382</v>
+        <v>2.35065710872162</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.723523786755841</v>
+        <v>-2.710325047801078</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.073648971783832</v>
+        <v>-1.060243844131001</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.778402296101419</v>
+        <v>-3.764945002391201</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.744019138755988</v>
+        <v>-3.730566850035878</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-9.164273749700889</v>
+        <v>-9.150717703349287</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-6.414552417424673</v>
+        <v>-6.424982053122825</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>46</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-4.667351363688233</v>
+        <v>-4.654829074012611</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-6.27892497665249</v>
+        <v>-6.266015167076439</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.325967596292493</v>
+        <v>-2.312960464874891</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.152111623271523</v>
+        <v>2.165090765669987</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.787603451677555</v>
+        <v>3.800714256052494</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.436693741041573</v>
+        <v>-2.423650844747208</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.521427458313781</v>
+        <v>-2.508361204013305</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-13.91917596066896</v>
+        <v>-13.9059772217142</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-12.59538810221862</v>
+        <v>-12.58198297456579</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-12.8001414265362</v>
+        <v>-12.78668413282598</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.316447662744373</v>
+        <v>-2.30289161639277</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.066726330468015</v>
+        <v>-2.077155966166167</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>59</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.340895947328619</v>
+        <v>-3.328373657652996</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-6.647384814530163</v>
+        <v>-6.634475004954112</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.2625925041776469</v>
+        <v>-0.2495853727600448</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.827254625807441</v>
+        <v>-1.814275483408977</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.365675840879554</v>
+        <v>-2.352565036504615</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.321596605310674</v>
+        <v>1.334639501605039</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.152967620436229</v>
+        <v>-2.139901366135753</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-9.39981203616685</v>
+        <v>-9.386631026871612</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-9.46081192234913</v>
+        <v>-9.447613183394367</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-6.921106598902483</v>
+        <v>-6.907701471249652</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3461989062709137</v>
+        <v>-0.3327416125606959</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.772930013786386</v>
+        <v>4.786382302506496</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.047590657078771</v>
+        <v>6.061146703430374</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.992227243592339</v>
+        <v>7.981797607894187</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>35</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>7.506561679790025</v>
+        <v>7.519083969465647</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-8.785594925485107</v>
+        <v>-8.772587794067505</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.798198935734753</v>
+        <v>-5.785219793336289</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-6.336620150806922</v>
+        <v>-6.323509346431983</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.3248924988055464</v>
+        <v>-0.311849602511181</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>2.460582895365505</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.980333242283621</v>
+        <v>1.993514251578858</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.9378095010415848</v>
+        <v>-0.9246107620868216</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.787934686069555</v>
+        <v>-1.774529558416724</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.849830867529953</v>
+        <v>-4.836373573819735</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-13.38687628161313</v>
+        <v>-13.37342399289302</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-10.94998803541517</v>
+        <v>-10.93643198906357</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-7.843123845996033</v>
+        <v>-7.853553481694185</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>29</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.7693003891754913</v>
+        <v>-0.7567780994998685</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.067401859929213</v>
+        <v>1.080311669505264</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-13.12057029494328</v>
+        <v>-13.10756316352568</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-6.093765438197806</v>
+        <v>-6.080786295799342</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-6.632186653269976</v>
+        <v>-6.619075848895037</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.5618070085836138</v>
+        <v>0.5748499048779792</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.971202570757626</v>
+        <v>-2.95813631645715</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.009889892529734823</v>
+        <v>0.02307090182497262</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.845441730485412</v>
+        <v>6.858640469440175</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>12.89186826959552</v>
+        <v>12.90527339724835</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>12.68711494527784</v>
+        <v>12.70057223898806</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.273222240554361</v>
+        <v>9.286674529274471</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>15.74951935374738</v>
+        <v>15.76307540009898</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>15.99924068602367</v>
+        <v>15.98881105032552</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>22</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-11.58434741111913</v>
+        <v>-11.57182512144351</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-13.19592102408332</v>
+        <v>-13.18301121450727</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-22.68169882158894</v>
+        <v>-22.66869169017134</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-22.55144568898151</v>
+        <v>-22.53846654658304</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-9.453503267690039</v>
+        <v>-9.440392463315099</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-18.24697042088354</v>
+        <v>-18.23392752458917</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-18.33170413815574</v>
+        <v>-18.31863788385527</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-14.25343299148264</v>
+        <v>-14.2402519821874</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-9.768978332210459</v>
+        <v>-9.755779593255696</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-6.073648971783904</v>
+        <v>-6.060243844131072</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.244019138755924</v>
+        <v>-6.230566850035814</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-6.414552417424666</v>
+        <v>-6.424982053122818</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>19</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-5.125017267578322</v>
+        <v>-5.112494977902699</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-11.99974877527942</v>
+        <v>-11.98683896570337</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.868301692402326</v>
+        <v>-1.855294560984724</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.738048559794969</v>
+        <v>-1.725069417396504</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-12.80278556434076</v>
+        <v>-12.78967475996582</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-17.76850152136186</v>
+        <v>-17.7554586250675</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-2.063761554423692</v>
+        <v>-2.050695300123216</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-18.32041863741572</v>
+        <v>-18.30723762812048</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-18.38141852359794</v>
+        <v>-18.36821978464318</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-13.96838581388903</v>
+        <v>-13.9549806862362</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-3.646823348733001</v>
+        <v>-3.633366055022783</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.650717703349201</v>
+        <v>1.664169992069311</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.493620987141149</v>
+        <v>6.507177033492752</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>6.743342319417579</v>
+        <v>6.732912683719427</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>19</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1381406271584424</v>
+        <v>0.1506629168340652</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>9.052882803667806</v>
+        <v>9.065792613243858</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>24.44748778128174</v>
+        <v>24.46049491269934</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>14.05142512441571</v>
+        <v>14.06440426681417</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.249846014606689</v>
+        <v>8.262956818981628</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.284130057585436</v>
+        <v>3.297172953879802</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.462554235049993</v>
+        <v>8.475620489350469</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.732212941531685</v>
+        <v>2.745393950826923</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>13.19752884482296</v>
+        <v>13.21072758377773</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.084245765058199</v>
+        <v>7.09765089271103</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.879492440740684</v>
+        <v>6.892949734450902</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.913875598086115</v>
+        <v>6.927327886806225</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.75677888187814</v>
+        <v>11.77033492822974</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>12.00650021415434</v>
+        <v>11.99607057845619</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>10</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-14.90804872223563</v>
+        <v>-14.89493791786069</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-24.61060678451983</v>
+        <v>-24.59756388822547</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-14.69534050179211</v>
+        <v>-14.68227424749163</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-15.16252390057368</v>
+        <v>-15.14934289127844</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-15.22352378675591</v>
+        <v>-15.21032504780115</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3.92635102821616</v>
+        <v>3.939756155868992</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-16.27840229610142</v>
+        <v>-16.2649450023912</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.244019138756059</v>
+        <v>-6.230566850035949</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-46.66427374970096</v>
+        <v>-46.65071770334936</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-36.4145524174246</v>
+        <v>-36.42498205312275</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-13.60454943132108</v>
+        <v>-13.59202714164546</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-20.7716785998409</v>
+        <v>-20.75876879026485</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-21.16654730643749</v>
+        <v>-21.15354017501989</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-21.03629417382999</v>
+        <v>-21.02331503143153</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-16.0191598333466</v>
+        <v>-16.00604902897166</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-21.2772734511865</v>
+        <v>-21.26423055489214</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-21.36200716845878</v>
+        <v>-21.34894091415831</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-44.0514127894625</v>
+        <v>-44.03823178016727</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-33.00130156453373</v>
+        <v>-32.98810282557896</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-28.29587119400606</v>
+        <v>-28.28246606635323</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-34.05618007387915</v>
+        <v>-34.04272278016894</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-39.57735247208925</v>
+        <v>-39.56390018336913</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-45.55316263858974</v>
+        <v>-45.53960659223814</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-50.85899686186901</v>
+        <v>-50.86942649756716</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Realized VOL-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Realized VOL-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2579142547323272</v>
+        <v>-0.2581510085509677</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1216297239855777</v>
+        <v>-0.1219091111378816</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3077515759722473</v>
+        <v>-0.3079878778546927</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3353976783124679</v>
+        <v>-0.3356266096927527</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3470313585768992</v>
+        <v>-0.3472606562468599</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3787085457722768</v>
+        <v>-0.37892852505599</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.3278337731402843</v>
+        <v>-0.3280668110924196</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.3901303616602476</v>
+        <v>-0.3903509656605522</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.3398028565233489</v>
+        <v>-0.3400362568075082</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3194863860835468</v>
+        <v>-0.3197297682436187</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2901583578207365</v>
+        <v>-0.2904102325577043</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3155527007354166</v>
+        <v>-0.3157982975009759</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.330041943770965</v>
+        <v>-0.3302865421537931</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3606308487971503</v>
+        <v>-0.3602920261685725</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3930</v>
+        <v>3931</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2235930247496682</v>
+        <v>-0.2243237384451007</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.122262060013405</v>
+        <v>-0.1230430315363051</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1735675212729717</v>
+        <v>-0.1743417985612297</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.156429537620177</v>
+        <v>-0.1572065987156321</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.300280253080885</v>
+        <v>-0.3010292884189312</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2429074447534489</v>
+        <v>-0.2436669600711099</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2630316371743788</v>
+        <v>-0.263787706100068</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.4115076404110098</v>
+        <v>-0.4122334170594257</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5094195936174089</v>
+        <v>-0.5101217957686259</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5576347369083976</v>
+        <v>-0.5583378720852679</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.6211432063480515</v>
+        <v>-0.6218336653296888</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.6743344998953589</v>
+        <v>-0.6750112944803206</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.6988705444096155</v>
+        <v>-0.699547815251627</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.714806870350813</v>
+        <v>-0.7139670442191672</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3709</v>
+        <v>3710</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.5321271971578554</v>
+        <v>-0.5335617463549269</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.6247646878100781</v>
+        <v>-0.6262235636841567</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.4676225752546941</v>
+        <v>-0.4691363409251039</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.5917302229471275</v>
+        <v>-0.5932075045498095</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.9005177916276423</v>
+        <v>-0.9019290445074972</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.776869899935491</v>
+        <v>-0.7783062228139528</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.7932952918889811</v>
+        <v>-0.7947305294394482</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.788365084961228</v>
+        <v>-0.7898165188348827</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.8885749445372753</v>
+        <v>-0.8900020329962999</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.943026833351297</v>
+        <v>-0.944465707351263</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.9712902271359027</v>
+        <v>-0.9727284658978022</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.9758973387020973</v>
+        <v>-0.9773340914151945</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.084758924903042</v>
+        <v>-1.0861798429343</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.170551338966796</v>
+        <v>-1.168917363095801</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.7092533359108018</v>
+        <v>-0.7115096378402939</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.4499576784626313</v>
+        <v>-0.452364755627876</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1725455926414341</v>
+        <v>-0.1750516922481324</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2553417928776085</v>
+        <v>-0.2578194587380054</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4925014230071412</v>
+        <v>-0.4949379178605469</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.4653809411807828</v>
+        <v>-0.4678125306947436</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.506035383118963</v>
+        <v>-0.5084606397157643</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.4428442667063308</v>
+        <v>-0.4453108638262719</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.4595752889018385</v>
+        <v>-0.4620412949407324</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.4926529786527638</v>
+        <v>-0.495150854145308</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.7387515660699293</v>
+        <v>-0.741189993805051</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.7457373518144053</v>
+        <v>-0.7481734918910092</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.9782239072488679</v>
+        <v>-0.9806146105657803</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.056386228312853</v>
+        <v>-1.054028171713419</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3217</v>
+        <v>3218</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4488286547824671</v>
+        <v>-0.4363063651068444</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1397083396178544</v>
+        <v>-0.1267985300418033</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.224787702967852</v>
+        <v>-0.2117805715502499</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5115549939931938</v>
+        <v>-0.5152605085071116</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.351322125831274</v>
+        <v>-0.3551176513591585</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.5330874046748661</v>
+        <v>-0.5368075336067406</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.5700303280948376</v>
+        <v>-0.5737471157086844</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.5239883746660681</v>
+        <v>-0.5277548019483547</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6301035508775783</v>
+        <v>-0.6338435088622703</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.6560767892318395</v>
+        <v>-0.6598714046524208</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.8125637867846507</v>
+        <v>-0.8163265609133958</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.8541465075040406</v>
+        <v>-0.8578960425824604</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.101812593703379</v>
+        <v>-1.105517330562705</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.270007810648103</v>
+        <v>-1.266498522979809</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2120032801542422</v>
+        <v>-0.1994809904786194</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.5449358202218022</v>
+        <v>0.5578456297978533</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.9511817078432472</v>
+        <v>0.9641888392608493</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.046603771136922</v>
+        <v>1.059582913535387</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.239635011655139</v>
+        <v>1.252745816030078</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.9294629018913199</v>
+        <v>0.9231605980162598</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.6898111189816802</v>
+        <v>0.6835794110449598</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.5208791677667008</v>
+        <v>0.5146515318655744</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3397828055007963</v>
+        <v>0.3336080065921507</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.06731404287072706</v>
+        <v>0.06113739060913304</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.02177222396839085</v>
+        <v>0.01558535350551438</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.3431811499291726</v>
+        <v>-0.3492404975053418</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.7439104943743118</v>
+        <v>-0.7498797145224714</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.138521669695734</v>
+        <v>-1.133329939954741</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.01922237320646047</v>
+        <v>0.03174466288208322</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.6281396055869735</v>
+        <v>0.6410494151630246</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.012390493848187</v>
+        <v>1.025397625265789</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.9868197074841305</v>
+        <v>0.9997988498825947</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.149606127783983</v>
+        <v>1.162716932158922</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.118153932549539</v>
+        <v>1.109487144108002</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.9944490539366555</v>
+        <v>1.007515308237132</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.016813331395198</v>
+        <v>1.008100600537688</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.8607195829788736</v>
+        <v>0.8520531198401784</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.578711543237624</v>
+        <v>0.5700213664774125</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.74735882802036</v>
+        <v>0.7385665075580761</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3744892564021498</v>
+        <v>0.3658422053895691</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.06271124970088948</v>
+        <v>-0.0712565553602218</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.3379599985109607</v>
+        <v>-0.3312320531227542</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2018625890882007</v>
+        <v>-0.1893402994125779</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.7182093675678018</v>
+        <v>0.731119177143853</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.065374707239215</v>
+        <v>1.078381838656817</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.064680655211191</v>
+        <v>1.077659797609655</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.050048178681138</v>
+        <v>1.063158983056077</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.9982976240353878</v>
+        <v>1.011340520329753</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.7389676605824036</v>
+        <v>0.7520339148828796</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.5773276926171391</v>
+        <v>0.5905087019123769</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.497000230711329</v>
+        <v>0.4858774838444191</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1954641780632542</v>
+        <v>0.1842976405851502</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4086606409615214</v>
+        <v>0.3973529443104127</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.03057640125275185</v>
+        <v>0.01943314996412226</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1900830235416535</v>
+        <v>-0.2012205455005827</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.8346837084530421</v>
+        <v>-0.8256819656336845</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>2001</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1984859071080649</v>
+        <v>0.2110081967836877</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.7803320349214786</v>
+        <v>0.7932418444975298</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.033519160827382</v>
+        <v>1.046526292244984</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.712127228629299</v>
+        <v>1.725106371027763</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.672210500097506</v>
+        <v>1.685321304472446</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.321596605310674</v>
+        <v>1.334639501605039</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8879097474601352</v>
+        <v>0.9009760017606112</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.5204272459867099</v>
+        <v>0.5336082552819477</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.9360772107503195</v>
+        <v>0.9212801366455139</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.7626783735255387</v>
+        <v>0.747736205744296</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.335177334452752</v>
+        <v>1.319885336930156</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.8837616572032658</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8069906181152007</v>
+        <v>0.7918397392081573</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.1071867130101793</v>
+        <v>0.09675707731202721</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>1748</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1505811773528265</v>
+        <v>-0.1380588876772038</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.523559495397194</v>
+        <v>0.5364693049732452</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.6429765030863166</v>
+        <v>0.6559836345039187</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.116086778550958</v>
+        <v>1.129065920949422</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9205227063359374</v>
+        <v>0.9336335107108766</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.8751075011944494</v>
+        <v>0.8881503974888147</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5046594982078929</v>
+        <v>0.5177257525083689</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3231903851406699</v>
+        <v>0.3363713944359077</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.9228455671606142</v>
+        <v>0.903960666484565</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.134589014486188</v>
+        <v>1.115285029511071</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.902375735935202</v>
+        <v>1.91583302964542</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.593509465363006</v>
+        <v>1.606961754083116</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.57371252032199</v>
+        <v>1.587268566673593</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.079726758776765</v>
+        <v>1.069297123078613</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>1547</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.521880466299173</v>
+        <v>-0.5093581766235502</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1942168459085565</v>
+        <v>-0.1813070363325053</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1219680997249739</v>
+        <v>0.134975231142576</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5107861967797973</v>
+        <v>0.5237653391782615</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1662887050431152</v>
+        <v>0.1793995094180545</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1826817683595223</v>
+        <v>-0.1696388720651569</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.4613392089672885</v>
+        <v>-0.4482729546668125</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7992401255251309</v>
+        <v>-0.7860591162298931</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.4077513239246215</v>
+        <v>-0.3945525849698583</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.5468228567224287</v>
+        <v>-0.5334177290695976</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.282683676749258</v>
+        <v>0.2961409704594757</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.05850186964737247</v>
+        <v>0.07195415836748253</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1553771875971037</v>
+        <v>0.1689332339487066</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1465335554260747</v>
+        <v>0.1361039197279226</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>1260</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.04624421947256963</v>
+        <v>0.05876650914819237</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.5335833617456629</v>
+        <v>-0.5206735521696118</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2935314334216201</v>
+        <v>-0.280524302004018</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2335470960112787</v>
+        <v>0.2465262384097429</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.01258619839943265</v>
+        <v>0.02569700277437192</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.07193289801984548</v>
+        <v>0.08497579431421087</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.0921658986175089</v>
+        <v>-0.07909964431703287</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.7974445354942503</v>
+        <v>-0.7842635261990125</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.06479362802574684</v>
+        <v>-0.05159488907098364</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.1212680194028835</v>
+        <v>-0.1078628917500524</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6263596086604863</v>
+        <v>0.6398169023707041</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1845522898154428</v>
+        <v>0.1980045785355529</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.161123075695933</v>
+        <v>0.1746791220475359</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.09338409051190411</v>
+        <v>0.08295445481375197</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>1030</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.06625385419055618</v>
+        <v>-0.05373156451493344</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.677827467154813</v>
+        <v>-1.664917657578762</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.490171901906741</v>
+        <v>-1.477164770489139</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.262831390658469</v>
+        <v>-1.249852248260005</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.9274661979636463</v>
+        <v>-0.914355393588707</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.435849502966434</v>
+        <v>-0.4228066066720686</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.5205832202387128</v>
+        <v>-0.5075169659382368</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.376116133583317</v>
+        <v>-1.362935124288079</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.6604169906394119</v>
+        <v>-0.6472182516846487</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.8309305251818913</v>
+        <v>-0.8175253975290602</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.2589848203732714</v>
+        <v>-0.2455275266630537</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.9042133135132744</v>
+        <v>-0.8907610247931643</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.9361184098950588</v>
+        <v>-0.9225623635434559</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.6863970776187713</v>
+        <v>-0.6968267133169235</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>909</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4582347998579408</v>
+        <v>-0.4457125101823181</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.069808412822198</v>
+        <v>-2.056898603246147</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.804611112818129</v>
+        <v>-1.791603981400527</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.9042809725098522</v>
+        <v>-0.891301830111388</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.442702187582022</v>
+        <v>-1.429591383207082</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.695315255366914</v>
+        <v>-1.682272359072549</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.340004968238752</v>
+        <v>-1.326938713938276</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.917199368120372</v>
+        <v>-1.904018358825134</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.8780892433015737</v>
+        <v>-0.8648905043468105</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.7381154184285066</v>
+        <v>-0.7247102907756755</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2672522693551329</v>
+        <v>0.2807095630653507</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.9084855854006548</v>
+        <v>-0.8950332966805448</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.218729195245437</v>
+        <v>-1.205173148893834</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.189029865169381</v>
+        <v>-1.199459500867533</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>797</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.301468433133437</v>
+        <v>-1.288946143457814</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.662101017239472</v>
+        <v>-2.649191207663421</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.053205608403196</v>
+        <v>-2.040198476985594</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.421070418079253</v>
+        <v>-1.408091275680789</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.834021118722319</v>
+        <v>-1.82091031434738</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.163931753152205</v>
+        <v>-2.15088885685784</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.621312898278937</v>
+        <v>-1.608246643978461</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.841319383635089</v>
+        <v>-2.828138374339851</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.149496183242739</v>
+        <v>-2.136297444287976</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.744916223979573</v>
+        <v>-1.731511096326741</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.8204349184351685</v>
+        <v>-0.8069776247249507</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.413404333235285</v>
+        <v>-1.399952044515175</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.331776886463757</v>
+        <v>-1.318220840112154</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.08205555418747</v>
+        <v>-1.092485189885622</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>703</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.9998394581900598</v>
+        <v>-0.9873171685144371</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.611413071154317</v>
+        <v>-2.598503261578266</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.868301692402405</v>
+        <v>-1.855294560984802</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.169058517120646</v>
+        <v>-1.156079374722182</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.138489689518565</v>
+        <v>-1.125378885143625</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.979027837151413</v>
+        <v>-1.965984940857048</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.063761554423692</v>
+        <v>-2.050695300123216</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.384430017216566</v>
+        <v>-3.371249007921328</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.876439860724624</v>
+        <v>-2.86324112176986</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.446337449735481</v>
+        <v>-2.43293232208265</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.939853220710233</v>
+        <v>-1.926395927000016</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.043450148713312</v>
+        <v>-3.029997859993202</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.32145724898966</v>
+        <v>-3.307901202638057</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.787240895376243</v>
+        <v>-2.797670531074395</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>619</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.7971539906461658</v>
+        <v>-0.784631700970543</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.247176715080535</v>
+        <v>-2.234266905504484</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.5418838707885953</v>
+        <v>-0.5288767393709932</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3961237044683443</v>
+        <v>0.4091028468668085</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4653992876636011</v>
+        <v>-0.4522884832886618</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.460364458187037</v>
+        <v>-1.447321561892672</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.706649063989204</v>
+        <v>-1.693582809688728</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.304688682479913</v>
+        <v>-3.291507673184675</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.719485014542663</v>
+        <v>-2.7062862755879</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.923406645451045</v>
+        <v>-2.910001517798214</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.997303750059416</v>
+        <v>-1.983846456349198</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.416878589482963</v>
+        <v>-3.403426300762852</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.867827869248551</v>
+        <v>-2.854271822896948</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.456555648442375</v>
+        <v>-2.466985284140527</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>535</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3439056099295996</v>
+        <v>-0.3313833202539769</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.955479222893857</v>
+        <v>-1.942569413317806</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.602684378088576</v>
+        <v>-1.589677246670973</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5836435208740625</v>
+        <v>0.5966226632725267</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5155253577495102</v>
+        <v>-0.502414553374571</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9657469714357205</v>
+        <v>-0.9527040751413551</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.424312464408935</v>
+        <v>-1.411246210108459</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-3.760654741695113</v>
+        <v>-3.747473732399875</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.139411637223198</v>
+        <v>-2.126212898268435</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.428789158699729</v>
+        <v>-2.415384031046898</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.259710707316366</v>
+        <v>-2.246253413606148</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.159906989223273</v>
+        <v>-3.146454700503163</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.645582160915836</v>
+        <v>-2.632026114564233</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.208944940789095</v>
+        <v>-2.219374576487247</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>466</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5621078481069759</v>
+        <v>-0.5495855584313531</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.388273735749337</v>
+        <v>-2.375363926173286</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.568550167667823</v>
+        <v>-2.555543036250221</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5069665629573166</v>
+        <v>-0.4939874205588524</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.689164602063819</v>
+        <v>-1.67605379768888</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.464684037738714</v>
+        <v>-2.451641141444348</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.549417755010992</v>
+        <v>-2.536351500710516</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-3.077601039974795</v>
+        <v>-3.064402301020031</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.640172576934049</v>
+        <v>-2.626767449281218</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.201149077217295</v>
+        <v>-2.187691783507077</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.239727293262419</v>
+        <v>-3.226275004542309</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.801612805494884</v>
+        <v>-2.788056759143281</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.337299198540478</v>
+        <v>-2.34772883423863</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>381</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.574803149606296</v>
+        <v>-1.562280859930674</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.611573612964257</v>
+        <v>-1.598663803388206</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6941063615555976</v>
+        <v>-0.6810992301379954</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.4860155374560975</v>
+        <v>0.4989946798545617</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8398072524192202</v>
+        <v>-0.8266964480442809</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.067299697905653</v>
+        <v>-1.054256801611288</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.1021646487737371</v>
+        <v>-0.08909839447326107</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.456487155166784</v>
+        <v>-3.443306145871546</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.779954232950132</v>
+        <v>-3.766755493995369</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.530341885169662</v>
+        <v>-2.516936757516831</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6353576766788436</v>
+        <v>-0.6219003829686258</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6009745193334126</v>
+        <v>-0.5875222306133026</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.4962947470762202</v>
+        <v>-0.4827387007246173</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.2783609684021684</v>
+        <v>0.2679313327040163</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>341</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.053555622262763</v>
+        <v>-2.041033332587141</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.905598443438166</v>
+        <v>-1.892688633862115</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2476812262810881</v>
+        <v>-0.234674094863486</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.4690821702560299</v>
+        <v>0.4820613126544941</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.06933904481613951</v>
+        <v>-0.05622824044120023</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6516625029949097</v>
+        <v>-0.6386196067005443</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1433691756272424</v>
+        <v>0.1564354299277184</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-4.13613093869678</v>
+        <v>-4.122949929401543</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.903875692914269</v>
+        <v>-3.890676953959506</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.701214954188536</v>
+        <v>-2.687809826535705</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.2666720908228299</v>
+        <v>-0.2532147971126122</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.232288933477399</v>
+        <v>-0.2188366447572889</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.5204769834369429</v>
+        <v>0.5340330297885458</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.063453447678043</v>
+        <v>1.053023811979891</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>295</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.645980693091332</v>
+        <v>-1.633458403415709</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.223656000970841</v>
+        <v>-1.21074619139479</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.0763905466698489</v>
+        <v>0.08939767808745103</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.2066436792773487</v>
+        <v>0.2196228216758129</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6707605866422739</v>
+        <v>-0.6576497822673346</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3733186489266132</v>
+        <v>-0.3602757526322478</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.5588967863434746</v>
+        <v>0.5719630406439506</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.976083222607507</v>
+        <v>-3.962902213312269</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.342167854552521</v>
+        <v>-2.328969115597758</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.158394734495701</v>
+        <v>-1.14498960684287</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.687699398813834</v>
+        <v>1.701156692524052</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.7051334036168981</v>
+        <v>0.7185856923370082</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.9628448943669099</v>
+        <v>0.9764009407185128</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.551549277490651</v>
+        <v>1.541119641792498</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>236</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.22225187953201</v>
+        <v>-1.209729589856387</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1322762024189856</v>
+        <v>0.1451860119950368</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1611363093817175</v>
+        <v>0.1741434407993196</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.7151182555485391</v>
+        <v>0.7280973979470033</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2470317730829521</v>
+        <v>-0.2339209687080128</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.7970474624859349</v>
+        <v>-0.7840045661915696</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.236862888038395</v>
+        <v>1.249929142338871</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.620151019217673</v>
+        <v>-2.606970009922435</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5625068376033724</v>
+        <v>-0.5493080986486092</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2822832316059944</v>
+        <v>0.2956883592588255</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.196173975085024</v>
+        <v>2.209631268795242</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.3118157489254827</v>
+        <v>-0.2983634602053726</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.3083415463110555</v>
+        <v>-0.2947854999594526</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.05862021403476803</v>
+        <v>-0.06904984973292017</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>201</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.742194539115445</v>
+        <v>-2.729672249439822</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3736686495921404</v>
+        <v>-0.3607588400160893</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.719024832865991</v>
+        <v>1.732031964283593</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.84927796547349</v>
+        <v>1.862257107871955</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.813344312590381</v>
+        <v>0.8264551169653203</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.8792635009377392</v>
+        <v>-0.8662206046433738</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.026052533033763</v>
+        <v>1.039118787334239</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.421230368235307</v>
+        <v>-3.408049358940069</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4971556275519404</v>
+        <v>-0.4839568885971772</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.6427689386639202</v>
+        <v>0.6561740663167512</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.423090241212009</v>
+        <v>3.436547534922227</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.964936085124613</v>
+        <v>1.978388373844723</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.544681474179711</v>
+        <v>1.558237520531314</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.296890368645052</v>
+        <v>1.2864607329469</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>172</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.074833669047187</v>
+        <v>-3.062311379371565</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.6166398401509809</v>
+        <v>-0.6037300305749298</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.221049592787324</v>
+        <v>4.234056724204926</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.1885120277204</v>
+        <v>3.201491170118864</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.068695463811018</v>
+        <v>2.081806268185957</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.12223469149658</v>
+        <v>-1.109191795202214</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.700008335417195</v>
+        <v>1.713074589717671</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-3.999733202899186</v>
+        <v>-3.986552193603949</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.735151693732661</v>
+        <v>-1.721952954777898</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.422486181086171</v>
+        <v>-1.40908105343334</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.861132587619515</v>
+        <v>1.874589881329733</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.732725047290522</v>
+        <v>0.7461773360106321</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.8503202613287968</v>
+        <v>-0.8367642149771939</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.181994277889721</v>
+        <v>-1.192423913587874</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>150</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.826771653543304</v>
+        <v>-1.814249363867681</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.228321400159103</v>
+        <v>1.241231209735155</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.166786026895849</v>
+        <v>8.179793158313451</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.963705826170006</v>
+        <v>6.97668496856847</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.758617944431172</v>
+        <v>3.771728748806112</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.389393215480176</v>
+        <v>1.402436111774541</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.637992831541226</v>
+        <v>4.651059085841702</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.495857233906946</v>
+        <v>-2.482676224611708</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.5568571200892478</v>
+        <v>-0.5436583811344846</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.7403156384505039</v>
+        <v>-0.7269105107976728</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.054931037231917</v>
+        <v>3.068388330942135</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.755980861244005</v>
+        <v>1.769433149964115</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.002392916965774816</v>
+        <v>0.01594896331737772</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4145524174245949</v>
+        <v>-0.4249820531227471</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>131</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.348400152271047</v>
+        <v>-1.335877862595424</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.146896463772329</v>
+        <v>3.15980627334838</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>9.622256764809322</v>
+        <v>9.635263896226924</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.225792340164929</v>
+        <v>8.238771482563394</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.160653567840846</v>
+        <v>6.173764372215786</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.168019169678644</v>
+        <v>4.181062065973009</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.610003009658271</v>
+        <v>5.623069263958747</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2006918395049055</v>
+        <v>-0.1875108302096677</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.028384610190649</v>
+        <v>2.041583349145412</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.178259425162722</v>
+        <v>1.191664552815553</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.026941215348963</v>
+        <v>4.04039850905918</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.77124803681653</v>
+        <v>1.78470032553664</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.9390829100062277</v>
+        <v>-0.9255268636546248</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.452720356355897</v>
+        <v>-1.463149992054049</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>112</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.600581177352836</v>
+        <v>-1.588058887677214</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.144988066825768</v>
+        <v>2.157897876401819</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.107262217372039</v>
+        <v>7.120269348789641</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7.237515349979539</v>
+        <v>7.250494492378003</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.806236992050216</v>
+        <v>5.819347796425156</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.3179646440516</v>
+        <v>4.331007540345965</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.126088069636459</v>
+        <v>5.139154323936935</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.6982381862879024</v>
+        <v>-0.6850571769926646</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.1336190703869491</v>
+        <v>0.1468178093417123</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1763510282161604</v>
+        <v>0.1897561558689915</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>3.543026275327151</v>
+        <v>3.556483569037368</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.09284517827232</v>
+        <v>-3.079289131920717</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.735980988853171</v>
+        <v>-3.746410624551324</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>102</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.513046163347234</v>
+        <v>-1.500523873671611</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.75773316486498</v>
+        <v>2.770642974441031</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.26482524258212</v>
+        <v>7.277832373999722</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.39507837518962</v>
+        <v>7.408057517588084</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.837049316980192</v>
+        <v>7.850160121355131</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.154099097833111</v>
+        <v>7.167141994127476</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.069365380560832</v>
+        <v>7.082431634861308</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.7198290406028605</v>
+        <v>0.7330100498980983</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.639221311283301</v>
+        <v>1.652420050238064</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1912960306073686</v>
+        <v>-0.1778909029545375</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.486303586251523</v>
+        <v>5.499760879961741</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1.599118116145981</v>
+        <v>1.612570404866091</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>1.178863505201079</v>
+        <v>1.192419551552682</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.532199476248131</v>
+        <v>-0.5426291119462832</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>7.799749971587673</v>
+        <v>7.812659781163724</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>13.35726221737204</v>
+        <v>13.37026934878964</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>13.48751534997954</v>
+        <v>13.500494492378</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>12.94909413490737</v>
+        <v>12.96220493928231</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>13.24653607262303</v>
+        <v>13.2595789689174</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13.16180235535075</v>
+        <v>13.17486860965123</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>10.31366657561687</v>
+        <v>10.32684758491211</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9.06219049895838</v>
+        <v>9.075389237913143</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.831112932978066</v>
+        <v>5.844518060630897</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>13.95969294199381</v>
+        <v>13.97315023570403</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>11.19286910744197</v>
+        <v>11.20642515379357</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Realized VOL-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Realized VOL-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.98275215598051</v>
+        <v>12.99527444565613</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.37117854301625</v>
+        <v>11.3840883525923</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>18.1191669792768</v>
+        <v>18.1321741106944</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>20.63037249283668</v>
+        <v>20.64335163523514</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>21.2824274682407</v>
+        <v>21.29553827261564</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>23.96082178690874</v>
+        <v>23.9738646832031</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22.68561187916027</v>
+        <v>22.69867813346075</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>24.59938086133116</v>
+        <v>24.6125618706264</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>23.34790478467266</v>
+        <v>23.36110352362742</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>22.49777959964473</v>
+        <v>22.51118472729756</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>21.10255008485096</v>
+        <v>21.11600737856118</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>22.32740943267258</v>
+        <v>22.34086172139269</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>23.09763101220388</v>
+        <v>23.11118705855549</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>23.34735234448017</v>
+        <v>23.33692270878202</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>234</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.916818090046434</v>
+        <v>3.929340379722056</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.014646186483894</v>
+        <v>4.027555996059945</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.04712790723773</v>
+        <v>4.060135038655332</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.17738103984523</v>
+        <v>4.190360182243694</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.630412816226048</v>
+        <v>6.643523620600988</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.07315389924085</v>
+        <v>6.086196795535216</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.84312103666943</v>
+        <v>6.856187290969906</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.940040201990492</v>
+        <v>8.953221211285729</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>11.01579245256033</v>
+        <v>11.02899119151509</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11.87506897693412</v>
+        <v>11.88847410458695</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.95236693466781</v>
+        <v>12.96582422837803</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>13.84145094671409</v>
+        <v>13.8549032354342</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>14.27589719047005</v>
+        <v>14.28945323682166</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>14.09826809539591</v>
+        <v>14.08783845969776</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>455</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.429638602866945</v>
+        <v>4.442160892542567</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.114768286605987</v>
+        <v>6.127678096182038</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.401218261328083</v>
+        <v>4.414225392745685</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.168874354687581</v>
+        <v>8.181985159062521</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.367415193502147</v>
+        <v>7.380458089796512</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.722241915790306</v>
+        <v>7.735308170090782</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.474838736789025</v>
+        <v>7.488019746084262</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.512739949507818</v>
+        <v>8.525938688462581</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.981296083161212</v>
+        <v>8.994701210814043</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.21610319840407</v>
+        <v>9.229560492114288</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.250486355749501</v>
+        <v>9.263938644469611</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.14891306348591</v>
+        <v>10.16246910983752</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>10.61841461554242</v>
+        <v>10.60798497984427</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>674</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.738015685724747</v>
+        <v>3.75053797540037</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.016649787894018</v>
+        <v>3.029559597470069</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.286469508597136</v>
+        <v>1.299476640014738</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.8618264987714</v>
+        <v>1.874805641169864</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.103820713966286</v>
+        <v>3.116931518341225</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.10452674663744</v>
+        <v>3.117569642931805</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.464896886931925</v>
+        <v>3.477963141232401</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.997713488150424</v>
+        <v>3.010894497445662</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.233449507012629</v>
+        <v>3.246648245967393</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.421899989640487</v>
+        <v>3.435305117293318</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.70082619054547</v>
+        <v>4.714283484255688</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>4.735209347890901</v>
+        <v>4.748661636611011</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.947002214690798</v>
+        <v>5.960558261042401</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.196723546967085</v>
+        <v>6.186293911268933</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>947</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.563463681897503</v>
+        <v>1.519083969465647</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.9582792060662797</v>
+        <v>0.9131665803006683</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.04394195790605</v>
+        <v>0.9983585591573316</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.124564678686731</v>
+        <v>2.137543821085195</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.586143463614562</v>
+        <v>1.599254267989501</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.305971884962744</v>
+        <v>2.31901478125711</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.538028030414864</v>
+        <v>2.55109428471534</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.282037873449617</v>
+        <v>2.295218882744855</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.749021091807968</v>
+        <v>2.762219830762731</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.849265494953222</v>
+        <v>2.862670622606053</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.383688516992564</v>
+        <v>3.397145810702781</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.523668295246125</v>
+        <v>3.537120583966235</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.370573135198796</v>
+        <v>4.384129181550399</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.831487709291352</v>
+        <v>4.8210580735932</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>1302</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.492779137676699</v>
+        <v>0.4647610926485157</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.8483069523313134</v>
+        <v>-0.876175630489449</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.892518676580643</v>
+        <v>-1.919823699924095</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.02887539664912</v>
+        <v>-2.056034867832345</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.450291425768512</v>
+        <v>-2.477439836509816</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.6920199949653</v>
+        <v>-1.678977098670934</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.08550947260624</v>
+        <v>-1.072443218305764</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.7846437162418169</v>
+        <v>-0.7714627069465791</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3080091938219667</v>
+        <v>-0.2948104548672035</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3011590159273752</v>
+        <v>0.3145641435802062</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4036253536681684</v>
+        <v>0.4170826473783862</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.206057666159531</v>
+        <v>1.219509954879641</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.091486618962698</v>
+        <v>2.105042665314301</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.878842359841137</v>
+        <v>2.868412724142985</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>1605</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.008966270520531339</v>
+        <v>-0.02902279651821971</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.7178149163936283</v>
+        <v>-0.7380648565174397</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.452616958178787</v>
+        <v>-1.472578915438362</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.351581458625674</v>
+        <v>-1.37157373789919</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.607924189234247</v>
+        <v>-1.627980855010527</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.497281753386581</v>
+        <v>-1.484238857092215</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.237396576558467</v>
+        <v>-1.257616713245056</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.330748199639032</v>
+        <v>-1.317567190343794</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.017916310120405</v>
+        <v>-1.004717571165642</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5596302801950515</v>
+        <v>-0.5462251525422204</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.8266889004627913</v>
+        <v>-0.8132316067525736</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2315580795659571</v>
+        <v>-0.218105790845847</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4696826365919478</v>
+        <v>0.4832386829435507</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.8440145607685494</v>
+        <v>0.8335849250703973</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>1879</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2637196861526974</v>
+        <v>0.2482837574889629</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.6302108721662734</v>
+        <v>-0.6456546156448368</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.155931595184832</v>
+        <v>-1.171223640979214</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.10356271693496</v>
+        <v>-1.118856432705407</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.082331400237614</v>
+        <v>-1.097805682066607</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.9689268270503959</v>
+        <v>-0.9843864174496915</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.5995958209410475</v>
+        <v>-0.6152886015586176</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4525717983915953</v>
+        <v>-0.4684918274485881</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3006924935148305</v>
+        <v>-0.2874937545600673</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.07323767004692172</v>
+        <v>0.0866427976997528</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.1847354520354259</v>
+        <v>-0.1712781583252081</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2754060874281521</v>
+        <v>0.2888583761482622</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5470088474252464</v>
+        <v>0.5605648937768493</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.275708359584449</v>
+        <v>1.265278723886297</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1673213234342938</v>
+        <v>-0.1788902478455867</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.5105418870912786</v>
+        <v>-0.5223186136949138</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.834597098968608</v>
+        <v>-0.8463205129615119</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.417597986868117</v>
+        <v>-1.429031951671263</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.377822603176881</v>
+        <v>-1.389402862510003</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.009498751278834</v>
+        <v>-1.021191022512504</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.5613913101061954</v>
+        <v>-0.5733176454602358</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.2641874865255573</v>
+        <v>-0.2763636764977662</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.6024516980313237</v>
+        <v>-0.5892529590765605</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.43594102353984</v>
+        <v>-0.4225358958870089</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.9641693940681506</v>
+        <v>-0.9507121003579329</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.56010046962475</v>
+        <v>-0.54664818090464</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4720371508099461</v>
+        <v>-0.4584811044583432</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.1272876195610664</v>
+        <v>0.1369403128661588</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.1229605261023394</v>
+        <v>0.1138121408000714</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1891009686235279</v>
+        <v>-0.198406202708199</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3555507428636062</v>
+        <v>-0.3648619667209019</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6567562200346089</v>
+        <v>-0.6659267152803139</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5126710911995929</v>
+        <v>-0.5220006241311808</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4404994352217315</v>
+        <v>-0.4498131659803164</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1311108446256455</v>
+        <v>-0.1405731739986606</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.03855695842484863</v>
+        <v>-0.04814503915115864</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.4301353570038486</v>
+        <v>-0.4169366180490854</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.577781203188799</v>
+        <v>-0.5643760755359679</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.131647438722332</v>
+        <v>-1.140978060242439</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.9090315457038756</v>
+        <v>-0.9184544068775438</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8926560417985385</v>
+        <v>-0.9021651806032125</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.5784597021928164</v>
+        <v>-0.5706171379386475</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2617</v>
+        <v>2618</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3202498927177828</v>
+        <v>0.3126985646765945</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2882935061563074</v>
+        <v>0.2805214505463027</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.02827765551075601</v>
+        <v>0.02054376057031959</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1633085121119251</v>
+        <v>-0.1709558229079349</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.04244632726945952</v>
+        <v>0.03463954692818305</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2846313107182681</v>
+        <v>0.2767696989794075</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.4875863274761869</v>
+        <v>0.4796305144131239</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6514295877984821</v>
+        <v>0.6433400355508994</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4591611865469076</v>
+        <v>0.4511312998923316</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5459618637751049</v>
+        <v>0.5377729369521305</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.05747556649399854</v>
+        <v>0.04943882057713012</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1897342022138488</v>
+        <v>0.1816468904221367</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1348095199706094</v>
+        <v>0.1266782493043976</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.100541201222704</v>
+        <v>0.1067215374043613</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.008008083665579591</v>
+        <v>-0.01347257611351438</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3874434852071147</v>
+        <v>0.3816723021817268</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2171004923046453</v>
+        <v>0.2113432269005457</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.0229600014159459</v>
+        <v>0.01727959406876778</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1211308177576456</v>
+        <v>0.1153572091126804</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1284042044911615</v>
+        <v>0.1226558165462421</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2342369629966257</v>
+        <v>0.2284400382226579</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5075791922098958</v>
+        <v>0.5016361537233394</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2250839822368746</v>
+        <v>0.2192282168036641</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2537237930029619</v>
+        <v>0.2477657811697824</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.06925196930403388</v>
+        <v>-0.07512381944759738</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1221198839556479</v>
+        <v>0.1161823759703111</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.134349313982419</v>
+        <v>0.1283600667814753</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1281473070933075</v>
+        <v>0.1326771551388575</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3134</v>
+        <v>3135</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.03277712306933722</v>
+        <v>0.02861382969437187</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.6947337756623924</v>
+        <v>0.6902302564463056</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5716614905948347</v>
+        <v>0.5671633638654754</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.5285913223532219</v>
+        <v>0.5241147512923732</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4212544912548069</v>
+        <v>0.416766916745047</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.2907299436787696</v>
+        <v>0.2863050268238538</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3508231403600703</v>
+        <v>0.3463699281926509</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6018073096174774</v>
+        <v>0.5972346318034454</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.3992860252861377</v>
+        <v>0.3947704936001202</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4591744826457287</v>
+        <v>0.4545697907845607</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.272442460035009</v>
+        <v>0.2678784520383672</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4842971877746294</v>
+        <v>0.4796658563715184</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4968107798046901</v>
+        <v>0.4921394395078522</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.3818738748536319</v>
+        <v>0.3852252834003664</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1381406271584424</v>
+        <v>0.1345627091413917</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7159247059442251</v>
+        <v>0.7120594431092826</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5827892928684975</v>
+        <v>0.5789361029109372</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3623786184109505</v>
+        <v>0.3585996450330668</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.5147453954115662</v>
+        <v>0.5108813776984036</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.6146460502947519</v>
+        <v>0.61076944510787</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5468422082017597</v>
+        <v>0.5429785873229491</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6792424287732217</v>
+        <v>0.6753045642703768</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4206479923851916</v>
+        <v>0.4167832012022288</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.385387542484338</v>
+        <v>0.3814739472800284</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.105882541222087</v>
+        <v>0.1020387349515488</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4339053316155201</v>
+        <v>0.429961081210287</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5224584370313039</v>
+        <v>0.5184563832334561</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.4825289957858487</v>
+        <v>0.4853373571966557</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3172125673639883</v>
+        <v>0.3141150253662701</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7632922988470696</v>
+        <v>0.7599688823189794</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5622863229289976</v>
+        <v>0.5589980512798078</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.4423357738553406</v>
+        <v>0.4390887577928737</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.5421882445891484</v>
+        <v>0.5388790794743628</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6486524747394355</v>
+        <v>0.6453271070352002</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5506583126714375</v>
+        <v>0.5473553821379937</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8113865648874068</v>
+        <v>0.8079777963327714</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6780183247506102</v>
+        <v>0.67464382264059</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5860959110402533</v>
+        <v>0.5826980301275952</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.368481976895616</v>
+        <v>0.3651350925361285</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5087264830902569</v>
+        <v>0.5053381944745041</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.4913081980425815</v>
+        <v>0.487899096888178</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4016043987322107</v>
+        <v>0.4039965692050345</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2123763027030989</v>
+        <v>0.2097314514800317</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6603206323310999</v>
+        <v>0.6574660974726285</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4540364109204234</v>
+        <v>0.4512203586205814</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3408305740812736</v>
+        <v>0.3380520960646365</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3369080500988062</v>
+        <v>0.3341027044385001</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5349683091671054</v>
+        <v>0.5321191088926938</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.5814761072044305</v>
+        <v>0.5786078510958603</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8224775415954113</v>
+        <v>0.8195152402095118</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.7487785790836767</v>
+        <v>0.7458330139236864</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.665167767032905</v>
+        <v>0.662202780219836</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.5633990895798746</v>
+        <v>0.5604518230056215</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.7874564604354646</v>
+        <v>0.7844446973082313</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.8458360134418044</v>
+        <v>0.842785039936885</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.7076665944216813</v>
+        <v>0.7096222218628014</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3545</v>
+        <v>3546</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1484953503914852</v>
+        <v>0.1462264252116512</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.519671789063608</v>
+        <v>0.5172289612809635</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1682858394192834</v>
+        <v>0.1659237927432144</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.03262284445411723</v>
+        <v>0.03030326628126545</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1848044010059198</v>
+        <v>0.1824179189889534</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.385171431072628</v>
+        <v>0.3827399947233232</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.4566865252349217</v>
+        <v>0.4542301150189161</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7090615683083925</v>
+        <v>0.7065129645774775</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.6356311428215591</v>
+        <v>0.6330993396953275</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6747308535190584</v>
+        <v>0.6721505220661754</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5141568921736663</v>
+        <v>0.5116117741655728</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.7619013574379778</v>
+        <v>0.7592865885210571</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6679315520475626</v>
+        <v>0.6653240220524594</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.567111898513339</v>
+        <v>0.5688137731603788</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3629</v>
+        <v>3630</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.0601036896747047</v>
+        <v>0.05820008255926012</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.412977630132545</v>
+        <v>0.4109181949081346</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.3078116679214915</v>
+        <v>0.305765876431181</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.01344476543903994</v>
+        <v>0.01148350336700332</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1771629325198703</v>
+        <v>0.1751362783472032</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.269789146192295</v>
+        <v>0.2677467219999414</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.3651655488129535</v>
+        <v>0.3630928132727291</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.6834183277620127</v>
+        <v>0.6812401670274539</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.4726787448896559</v>
+        <v>0.4705552823226427</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5186989500438486</v>
+        <v>0.5165310595563923</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.4947254572025486</v>
+        <v>0.4925556857453302</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.6273661545516447</v>
+        <v>0.6251600222108138</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.5533571042936032</v>
+        <v>0.5511550589751408</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.4606198063285021</v>
+        <v>0.4620702884750472</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3698</v>
+        <v>3699</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.07999202201583699</v>
+        <v>0.07835121084496421</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.423289953618216</v>
+        <v>0.4215060682638452</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3936216519520173</v>
+        <v>0.3918326911076946</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.1611168294062608</v>
+        <v>0.1593936950895483</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.3118056074111166</v>
+        <v>0.3100243259366451</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4352647751131968</v>
+        <v>0.4334585018473689</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.4733504563725361</v>
+        <v>0.4715303936308715</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.7770009374393467</v>
+        <v>0.7750835594638659</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.5420716763820863</v>
+        <v>0.5402149090023087</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4903704771626707</v>
+        <v>0.488500417278658</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4359992170031433</v>
+        <v>0.4341365751344668</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.5667916720548192</v>
+        <v>0.5648938362651279</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.5133418220752617</v>
+        <v>0.5114444588128819</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.426983547962088</v>
+        <v>0.4282215154092839</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3783</v>
+        <v>3784</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1672571487046639</v>
+        <v>0.1659104113934902</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.2823398454818928</v>
+        <v>0.2809221124397538</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1390228921216377</v>
+        <v>0.1376324205005304</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.04640202091471224</v>
+        <v>0.04503850924674424</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.1816137250218901</v>
+        <v>0.1802004950052591</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.2298047164034074</v>
+        <v>0.2283854788631459</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.1595407646986544</v>
+        <v>0.1581372534316046</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.472208218719075</v>
+        <v>0.4707098791701725</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.531492052737228</v>
+        <v>0.5299758231410578</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4090550155412132</v>
+        <v>0.4075491864920053</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.2192205248177643</v>
+        <v>0.2177589849338517</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2156902403721546</v>
+        <v>0.2142297690872041</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.2067621911024915</v>
+        <v>0.2052928646824128</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.1014401810422214</v>
+        <v>0.1025020906404635</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3823</v>
+        <v>3824</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.1916503137837751</v>
+        <v>0.1904418011049458</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.2887299181947398</v>
+        <v>0.2874599201974348</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.09062535918588566</v>
+        <v>0.08939767808745103</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.05249615576389033</v>
+        <v>0.05128069105152377</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.1023896911256799</v>
+        <v>0.1011486983669485</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1792653115386358</v>
+        <v>0.1780102245093929</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1349467044742028</v>
+        <v>0.1337006937769658</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.4916939108654148</v>
+        <v>0.4903437927947394</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.4974793480403292</v>
+        <v>0.4961257226349929</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3935577175289353</v>
+        <v>0.3922117462556187</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1774262454563456</v>
+        <v>0.1761315588839523</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.174281514838782</v>
+        <v>0.1729877762056233</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1087388026003708</v>
+        <v>0.1074522312912336</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.03326343400098608</v>
+        <v>0.0342229677977457</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3869</v>
+        <v>3870</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.134073271752932</v>
+        <v>0.1330422491463068</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.2108860312679184</v>
+        <v>0.2098041103018744</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.06197503033226326</v>
+        <v>0.06092345119328968</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.07739492129762482</v>
+        <v>0.07634132595678977</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.1461029023132525</v>
+        <v>0.1450208343951829</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.1482273655962345</v>
+        <v>0.1471498817590629</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.1034211081150076</v>
+        <v>0.1023530416494509</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.4245728736199368</v>
+        <v>0.423412526678284</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.3262955214526571</v>
+        <v>0.3251588231665892</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2392867369690705</v>
+        <v>0.2381557428591776</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.0232505964605636</v>
+        <v>0.02217092841179635</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.09801134432331793</v>
+        <v>0.09691248880709935</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.07991229681073264</v>
+        <v>0.07880955059026462</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.008295863785015456</v>
+        <v>0.009126474009036656</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3928</v>
+        <v>3929</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.08205013449695286</v>
+        <v>0.08123516175382406</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1081860363689131</v>
+        <v>0.1073396424510449</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.05711352118373014</v>
+        <v>0.05627369976860308</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.04885903422824356</v>
+        <v>0.0480228715895521</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1084613107845698</v>
+        <v>0.1076014422207052</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1658159797078085</v>
+        <v>0.1649456367935898</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.06958961256621166</v>
+        <v>0.0687420126709668</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2772320729901878</v>
+        <v>0.2763241989376368</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.1794764675029299</v>
+        <v>0.1785920848882228</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.131844415805169</v>
+        <v>0.130958800160883</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.01770556449385197</v>
+        <v>0.0168454350452194</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1681946017020266</v>
+        <v>0.1672962891144607</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.1695261993955768</v>
+        <v>0.168620719042579</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.1282174400092018</v>
+        <v>0.1288484380963837</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3963</v>
+        <v>3964</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1474067502125607</v>
+        <v>0.1466927197799492</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.1339817775175831</v>
+        <v>0.133249989077882</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.02076639719406614</v>
+        <v>-0.02146470332177586</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.002650411769415939</v>
+        <v>-0.003351937990821341</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.05166930394779001</v>
+        <v>0.05094680401208507</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1614909238659621</v>
+        <v>0.1607442688742324</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.09055370475701352</v>
+        <v>0.08982346089415927</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.2922506018199371</v>
+        <v>0.291463154061681</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1696213745344153</v>
+        <v>0.1688636647208952</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1149066117805617</v>
+        <v>0.1141513171593189</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.02525050588457844</v>
+        <v>-0.02597348739246286</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.04854076036129129</v>
+        <v>0.04779926191570638</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.07134683556652277</v>
+        <v>0.07059377206055473</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.05781699968364507</v>
+        <v>0.05836809823949807</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3992</v>
+        <v>3993</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.140768920738843</v>
+        <v>0.1401523668695361</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1407423125800094</v>
+        <v>0.1401076142295352</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1156687986516687</v>
+        <v>-0.1162441377238466</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.04678892645367938</v>
+        <v>-0.04738031580158264</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.00322345971901683</v>
+        <v>0.002613306527258885</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.1643932154801675</v>
+        <v>0.1637457843563936</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.06835042093857169</v>
+        <v>0.0677257525083661</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2902024626079793</v>
+        <v>0.2895168236503594</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.2180573991335066</v>
+        <v>0.2173888091273142</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2076323094974413</v>
+        <v>0.2069565561692102</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.06702949363574362</v>
+        <v>0.06638632894013341</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1155201702074606</v>
+        <v>0.1148649397012846</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1852128518518228</v>
+        <v>0.1845351759696925</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.1736239352808084</v>
+        <v>0.1740662814627711</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4014</v>
+        <v>4015</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.07671315731671768</v>
+        <v>0.07618426738024198</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.0678643708496125</v>
+        <v>0.06732176515275512</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2390110745534244</v>
+        <v>-0.2394815560432306</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1698263143203746</v>
+        <v>-0.1703129610381566</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.04849117811418324</v>
+        <v>-0.04901346458023426</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.06368461279493687</v>
+        <v>0.06313708120033823</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.03232135232680378</v>
+        <v>-0.03284610229023599</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.2106104277846015</v>
+        <v>0.2100204511737545</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1633883804498595</v>
+        <v>0.1628092805570631</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1732400277183999</v>
+        <v>0.1726499105343251</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.03227731554906654</v>
+        <v>0.03172000507520778</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.08068205646313942</v>
+        <v>0.08011276161460756</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1476814184186637</v>
+        <v>0.1470910615909489</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1375153454054896</v>
+        <v>0.1379071125061415</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4033</v>
+        <v>4034</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.05228585181177436</v>
+        <v>0.05182427092351816</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.01118089748089801</v>
+        <v>0.01071547402910511</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2466660007995074</v>
+        <v>-0.2470712833841162</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1771961443139531</v>
+        <v>-0.1776177020546683</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.1084445658772495</v>
+        <v>-0.108887954961709</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.02015887558639662</v>
+        <v>-0.02062178035807705</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.04187515525745056</v>
+        <v>-0.04233363873142792</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1234379711768199</v>
+        <v>0.122934336444402</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.07612950695384768</v>
+        <v>0.07563682394928151</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1066829578668873</v>
+        <v>0.1061751751854842</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.01495746603931991</v>
+        <v>0.01447040508960384</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.08807503720435506</v>
+        <v>0.08756991904242284</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1775705735514634</v>
+        <v>0.1770394218056097</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1686362758558388</v>
+        <v>0.1689693598668285</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4052</v>
+        <v>4053</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.05268714104463612</v>
+        <v>0.05228613375487612</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.05345263375490106</v>
+        <v>0.05303932781633591</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1311875558426863</v>
+        <v>-0.1315585477233014</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.110641785843768</v>
+        <v>-0.1110170578487839</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.06933904481613951</v>
+        <v>-0.06972866133667566</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.004695454470571292</v>
+        <v>-0.00509897810480453</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.002066296322787764</v>
+        <v>-0.00247129182660899</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.1356525410232337</v>
+        <v>0.1352099542500866</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.1375804774787355</v>
+        <v>0.1371367560431054</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1393687796954453</v>
+        <v>0.1389180981909064</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.04712174828821958</v>
+        <v>0.0466920784766458</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1200657157087335</v>
+        <v>0.119618106807529</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2318525764772517</v>
+        <v>0.2313740578741985</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2241445223582303</v>
+        <v>0.2244134563763822</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.04643898040352923</v>
+        <v>0.04607121186015206</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.04324530786651337</v>
+        <v>0.04286720155518964</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.117361612027139</v>
+        <v>-0.1177031598014295</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.09654302779200918</v>
+        <v>-0.09688897365265348</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1057888352298448</v>
+        <v>-0.1061363461513167</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.06515223906529144</v>
+        <v>-0.06550788233010962</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.03817657945246111</v>
+        <v>-0.03853960375698762</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.09804640424447797</v>
+        <v>0.09764654101457637</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.09981036618237482</v>
+        <v>0.09940946547318674</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1486825579751354</v>
+        <v>0.14826365525429</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.006960557527122546</v>
+        <v>0.006574918907375604</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1044060580944048</v>
+        <v>0.1039964955975847</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1164301636636154</v>
+        <v>0.1160145801152836</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1339458592863778</v>
+        <v>0.1342106616200454</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01359468473477676</v>
+        <v>-0.01389111602531301</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.04831594099437098</v>
+        <v>-0.04861324013861434</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2099759709856812</v>
+        <v>-0.2102361671997528</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1886984118088009</v>
+        <v>-0.1889632022129106</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1758403583323371</v>
+        <v>-0.1761115119925805</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1585519899992889</v>
+        <v>-0.1588258104558449</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1320911746572904</v>
+        <v>-0.1323720948497495</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.09644460541942834</v>
+        <v>-0.0967370679360684</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.04604520658455158</v>
+        <v>-0.04635050056668888</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.02331478923477448</v>
+        <v>0.02298749001832334</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.14320758632919</v>
+        <v>-0.1434954431355706</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.07057474875108483</v>
+        <v>-0.07088034501505547</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.0850039628839383</v>
+        <v>-0.08530859016947545</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.09102300565989907</v>
+        <v>-0.09075024719282965</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/volatility/realized_vol_14.xlsx
+++ b/workspaces/btc_daily_14days/volatility/realized_vol_14.xlsx
@@ -575,46 +575,46 @@
         <v>150</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.144651000458666</v>
+        <v>-1.173754417944359</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.09219283723001581</v>
+        <v>-0.09337469185506819</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-3.810406129205262</v>
+        <v>-3.810584056900673</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.011420364033185</v>
+        <v>-5.01194440551388</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.558830702457556</v>
+        <v>-1.510403609241422</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.923683271426192</v>
+        <v>-3.899793574057902</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.012607889258561</v>
+        <v>-1.964690145628026</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1831151439995722</v>
+        <v>0.2322901034042459</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.117338767566942</v>
+        <v>4.190517813607698</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.933393273100016</v>
+        <v>6.032656089817941</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.395093195620021</v>
+        <v>8.494942513378675</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.097976976670786</v>
+        <v>9.221623158139074</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>9.346820554830416</v>
+        <v>9.495478582735124</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.908351280210873</v>
+        <v>9.080350039776626</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>221</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.966956846828573</v>
+        <v>4.937924831501803</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.324014770583759</v>
+        <v>8.322913648364981</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.77447155967392</v>
+        <v>4.774363328575035</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.162084625921395</v>
+        <v>7.161650879978318</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.786473404289573</v>
+        <v>9.834969025492988</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.731498943892376</v>
+        <v>8.755460274536652</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.649324848601672</v>
+        <v>8.697291716619922</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.926378834465062</v>
+        <v>5.975574238835939</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.867053227374569</v>
+        <v>5.940233135998611</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.923717643013525</v>
+        <v>6.022973891070478</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.268753258234582</v>
+        <v>5.368591216816704</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.400181359946785</v>
+        <v>4.523816447627816</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.790971744489077</v>
+        <v>5.939624525509622</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.923434236470001</v>
+        <v>7.095432996036877</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>219</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.303041400564766</v>
+        <v>2.476989727724025</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.397644106718339</v>
+        <v>-3.676345454912742</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.15703364015495</v>
+        <v>-4.532799430144941</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.939507358106972</v>
+        <v>-5.312533552281749</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.389627780235791</v>
+        <v>-6.716905637504645</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-5.727774164312386</v>
+        <v>-5.285470785856717</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-5.358055575217392</v>
+        <v>-5.101027134241114</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-6.281456891597664</v>
+        <v>-6.232329769874156</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.711969779808982</v>
+        <v>-7.638857161622106</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.106831700693682</v>
+        <v>-8.007634558004064</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.663599726517809</v>
+        <v>-4.563795468216924</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.630300543191055</v>
+        <v>-4.506688341027662</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.768957131511996</v>
+        <v>-2.620315975917087</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.000324518876177</v>
+        <v>-2.828325759309514</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.955480816068274</v>
+        <v>-3.830418166576948</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.289991546602174</v>
+        <v>-4.002097803943542</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2578916542509049</v>
+        <v>-0.03421576656744918</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.776778703009263</v>
+        <v>2.487374702281429</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.143075711272438</v>
+        <v>-2.916905293162934</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.3454692252423328</v>
+        <v>0.2787736255853019</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2611066853583139</v>
+        <v>0.2176063382287481</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.526500831693312</v>
+        <v>0.4717617670743408</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.563085168061079</v>
+        <v>1.363645628430504</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.446500177107033</v>
+        <v>1.095745914779165</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.144485731303476</v>
+        <v>-0.0003562180211886812</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.5451860983108006</v>
+        <v>0.4235183987962401</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.491681920387073</v>
+        <v>0.2297408599335142</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.450475822335129</v>
+        <v>1.41125028308624</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.346252977953647</v>
+        <v>-2.247295463430632</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-5.648309036016215</v>
+        <v>-5.656105987338222</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-9.695725425500001</v>
+        <v>-9.821083717120906</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-13.21603999388083</v>
+        <v>-13.33144177460391</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-13.32219682638843</v>
+        <v>-13.54248734549356</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-12.31114207117478</v>
+        <v>-12.70808975539833</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-10.71381992161208</v>
+        <v>-11.08816032456883</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-8.934541657467427</v>
+        <v>-9.034459412083798</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-8.436135589836894</v>
+        <v>-8.511034433879608</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.47465501263504</v>
+        <v>-6.535998036681114</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-7.525520394663637</v>
+        <v>-7.580561367523515</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.960095551190342</v>
+        <v>-5.126478072144891</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.973659569219627</v>
+        <v>-4.121075774619072</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.340475010869291</v>
+        <v>-2.471470688514074</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.153070669037646</v>
+        <v>-2.181164456465936</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.145130246554757</v>
+        <v>-0.1459204889902068</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4470453007371802</v>
+        <v>0.4471836279582462</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.56468919390219</v>
+        <v>1.563909774436091</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.013385890981048</v>
+        <v>2.061502738747322</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.6510834877754306</v>
+        <v>-0.6262380582232225</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.053304736849327</v>
+        <v>-2.002683621132896</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.654423107740378</v>
+        <v>-3.784305855200444</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.046654336361478</v>
+        <v>-4.150225832758302</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.238344385703698</v>
+        <v>-4.316159676731168</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.092770271492931</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.390863333845182</v>
+        <v>-6.435817597428681</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.483461521305777</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.910130567974164</v>
+        <v>-7.897720135661359</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.876271027135999</v>
+        <v>1.837714262069625</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1104085260346821</v>
+        <v>-0.1077816636659392</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.5833468522296883</v>
+        <v>0.5854368697584036</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3501998480429336</v>
+        <v>0.3530020703932948</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.993335441827227</v>
+        <v>2.037665972919712</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.928330873878437</v>
+        <v>1.948132651158929</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.139013356440891</v>
+        <v>2.974433083672523</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.492097243813056</v>
+        <v>4.320194526187727</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.907080506286526</v>
+        <v>3.558584235891594</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.788139751111395</v>
+        <v>3.459393336236118</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.585333681222835</v>
+        <v>3.255252888699935</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.25595571160332</v>
+        <v>2.951100785485117</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.013041552161155</v>
+        <v>0.7443486560227441</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.793996049066948</v>
+        <v>3.529625402096002</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>285</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.000208162180037</v>
+        <v>-3.036427614360669</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2949526600396197</v>
+        <v>0.2926760022378687</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.302041306621987</v>
+        <v>1.302446785852979</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.468096670494312</v>
+        <v>-3.479949874686639</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.305075420993617</v>
+        <v>-3.267444629673726</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.25855864293986</v>
+        <v>-1.240273145942517</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2936963161428565</v>
+        <v>-0.2482976562205295</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.9900097324649693</v>
+        <v>1.040255548308402</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.571107457401112</v>
+        <v>-2.505488990653035</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.771634180058584</v>
+        <v>-3.680194764450555</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.079795538609261</v>
+        <v>-5.9895983698813</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.049062790335967</v>
+        <v>-5.931431632516407</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-7.173549070771422</v>
+        <v>-7.028343945045222</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.302175035578813</v>
+        <v>-7.48105346899461</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.622744416695291</v>
+        <v>2.568013175112881</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.567306663028937</v>
+        <v>2.547336089957163</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.74482101845603</v>
+        <v>3.716098101642459</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.843204026114513</v>
+        <v>5.799107142857181</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.878800606825145</v>
+        <v>6.872358001905219</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.419473311862554</v>
+        <v>4.41076852072419</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.548886814776097</v>
+        <v>3.568862431498687</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.896335657490965</v>
+        <v>1.931154671115387</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.04094193048477</v>
+        <v>1.112932061978547</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.791692031189754</v>
+        <v>-1.664021518836435</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.79757144910257</v>
+        <v>-2.649411966372568</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-4.112893557602966</v>
+        <v>-4.153745229007633</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.703850341462136</v>
+        <v>-4.939528155571374</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.622610511620735</v>
+        <v>-7.034233293556092</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.719652555108873</v>
+        <v>2.662301968216461</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.060847414425922</v>
+        <v>6.00523325744485</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.665933883260088</v>
+        <v>4.626273594253298</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.78777238861106</v>
+        <v>5.741379310344769</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6.738608635088987</v>
+        <v>6.72996268170818</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>9.029443929827075</v>
+        <v>8.973191550280745</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>7.952551623155173</v>
+        <v>7.927313786178487</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8.975177364585115</v>
+        <v>8.939313538110362</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>10.89799051723085</v>
+        <v>10.87278427872732</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>13.80455451968172</v>
+        <v>13.4972315599813</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>14.38182116676309</v>
+        <v>13.78570194988369</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>13.42117444349646</v>
+        <v>12.85864701237168</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>12.5035111523721</v>
+        <v>11.97087824836944</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>8.251634862300072</v>
+        <v>7.786425573438983</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>287</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.00356411415801</v>
+        <v>-3.032759908510641</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.308594740513314</v>
+        <v>1.307407954068658</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.959119523005668</v>
+        <v>1.958966133001347</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.740912610844902</v>
+        <v>1.740418118466899</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.8541910020000714</v>
+        <v>0.9027369217658432</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.2874593586087</v>
+        <v>-1.263501949659087</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.069033829373168</v>
+        <v>-2.021022150382848</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7939421944142637</v>
+        <v>-0.744694632020547</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.900220518184462</v>
+        <v>-1.826963408404765</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.40170725876515</v>
+        <v>-2.302359933470576</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.212680194028827</v>
+        <v>-1.112772158010152</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4814379301752538</v>
+        <v>-0.3577413091470092</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1437073837587235</v>
+        <v>0.2923969315365511</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3694430339852559</v>
+        <v>0.5414417935519182</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>230</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.5625622303352174</v>
+        <v>0.533366435982586</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.603550050314865</v>
+        <v>4.60236326387021</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.078343882951131</v>
+        <v>5.07819049294681</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6.947699461322102</v>
+        <v>6.947204968944099</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.235496864748143</v>
+        <v>4.284042784513915</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.358957850904915</v>
+        <v>2.382915259854528</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.839464882943147</v>
+        <v>1.887476561933468</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.807178847852065</v>
+        <v>1.856426410245781</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.615761908720692</v>
+        <v>2.689019018500389</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.070190938477637</v>
+        <v>3.16953826377221</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>4.604620215000153</v>
+        <v>4.704528251018829</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.073780976051125</v>
+        <v>5.19747759707937</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.08841273143328</v>
+        <v>5.237102279211108</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3.575017946877196</v>
+        <v>3.747016706443858</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>121</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.890984795911933</v>
+        <v>2.861789001559302</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.279798702848105</v>
+        <v>1.278611916403449</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.8850273180930657</v>
+        <v>0.8848739280887443</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.943425224269035</v>
+        <v>-3.943919716647038</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.956301751560886</v>
+        <v>3.004847671326658</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>9.038799748138167</v>
+        <v>9.062757157087781</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5.648304264905057</v>
+        <v>5.696315943895378</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.701896778143166</v>
+        <v>2.751144340536882</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.9880220596368261</v>
+        <v>1.061279169416522</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.514789298676369</v>
+        <v>-1.415441973381796</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.198829299912049</v>
+        <v>-4.098921263893374</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.8586660235896915</v>
+        <v>-0.7349694025614468</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.200521966072252</v>
+        <v>1.349211513850079</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.079150178282347</v>
+        <v>3.25114893784901</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>112</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>5.554798255179939</v>
+        <v>5.525602460827308</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.157897876401762</v>
+        <v>2.156711089957106</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.02258779406751188</v>
+        <v>-0.02274118407183323</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.786208778092337</v>
+        <v>2.785714285714334</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.355062082139504</v>
+        <v>1.403608001905276</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.652436111774534</v>
+        <v>1.676393520724147</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6748686096512273</v>
+        <v>0.722880288641548</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.672085680150154</v>
+        <v>4.721333242543871</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>8.182532095055947</v>
+        <v>8.255789204835644</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>6.439756155868992</v>
+        <v>6.539103481163565</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>8.02076928332319</v>
+        <v>8.120677319341866</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.698004578535553</v>
+        <v>2.821701199563798</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.4007177033491871</v>
+        <v>-0.2520281555713595</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.960696338837046</v>
+        <v>-1.788697579270384</v>
       </c>
     </row>
     <row r="20">
@@ -1303,150 +1303,150 @@
         <v>94</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.544745817768394</v>
+        <v>-3.573941612121025</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.028272336364076</v>
+        <v>-3.029459122808731</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.423043721119178</v>
+        <v>-3.4231971111235</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.292818577530817</v>
+        <v>-3.29331306990882</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-7.022597492328636</v>
+        <v>-6.974051572562864</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.533734100991424</v>
+        <v>-3.509776692041811</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.700704475912616</v>
+        <v>1.748716154902937</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.233635832125877</v>
+        <v>1.282883394519594</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.300313250071248</v>
+        <v>3.373570359850945</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.514224240975437</v>
+        <v>3.613571566270011</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>7.564842231651355</v>
+        <v>7.66475026767003</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>10.7907097457088</v>
+        <v>10.91440636673705</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>13.56204825409752</v>
+        <v>13.71073780187535</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>11.66012432985597</v>
+        <v>11.83212308942263</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 71.91</t>
+          <t>X ≈ 71.9</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.480916030534289</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.282578314074371</v>
+        <v>-5.312801105164716</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-11.62973065121037</v>
+        <v>-11.80410006908925</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-12.68998169809819</v>
+        <v>-11.67421602787457</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-6.085414108336742</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.788040078701655</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.958866700802183</v>
+        <v>-2.661070938640755</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.01984885732503</v>
+        <v>-3.917555742899566</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.082613298726066</v>
+        <v>1.356176651895204</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.503040240486435</v>
+        <v>-1.286988185884717</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2781858976549927</v>
+        <v>-0.009309253397873363</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-6.650717703349351</v>
+        <v>-5.282515960449651</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.234505862646635</v>
+        <v>-3.813958903312255</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 75.63</t>
+          <t>X ≈ 75.62</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-3.671392221010613</v>
+        <v>-4.274817707239926</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-3.505053615925327</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>6.227412205932424</v>
+        <v>5.512973101642523</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7852197933362888</v>
+        <v>-2.592436974789912</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1330331559557862</v>
+        <v>-0.7287449392711878</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-5.161841773393498</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.491798057015444</v>
+        <v>-2.869556686148364</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3874381293735425</v>
+        <v>-2.158918858296488</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-6.40080123827741</v>
+        <v>-6.901773820374395</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-6.54913181295408</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.312564050010316</v>
+        <v>-0.8709193193136997</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-5.040090659559688</v>
+        <v>-5.518634934889988</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.269765322396971</v>
+        <v>-5.91379286145375</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.044029672170304</v>
+        <v>-5.664747999438383</v>
       </c>
     </row>
     <row r="23">
@@ -1459,98 +1459,98 @@
         <v>69</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.142272375262785</v>
+        <v>2.562351943228911</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.9803616445177639</v>
+        <v>-0.4701005042456998</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.933416346719362</v>
+        <v>4.933262956714799</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>7.962192214945283</v>
+        <v>7.96169772256733</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>7.423902661849588</v>
+        <v>6.023173219296439</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>9.170552053803512</v>
+        <v>7.745234100434288</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6.187290969899678</v>
+        <v>4.786027286571148</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.720222326112847</v>
+        <v>5.769469888506727</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.209964807271405</v>
+        <v>4.283221917051009</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.9877800760151132</v>
+        <v>-0.8884327507204901</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.641756596594014</v>
+        <v>-1.092573198256538</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.607378444238741</v>
+        <v>-1.034406460891688</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.578253935233263</v>
+        <v>0.01971097486336504</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.352518285006887</v>
+        <v>0.268755836878654</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 83.09</t>
+          <t>X ≈ 83.08</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.989672204759728</v>
+        <v>3.303841663485144</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.856808005951123</v>
+        <v>-5.256079607717226</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-10.95746174364737</v>
+        <v>-10.3009803867296</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.944883658882503</v>
+        <v>-4.357142857142897</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-5.483173211978198</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-8.715210947048995</v>
+        <v>-8.061978572299111</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-13.50580365925634</v>
+        <v>-12.77379745222224</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-12.79640171480779</v>
+        <v>-12.07683951493117</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.0837925992576416</v>
+        <v>0.6768855503506046</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.119067373542741</v>
+        <v>-2.472524425813184</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-9.20612147297944</v>
+        <v>-9.653409059395813</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-15.05409626180055</v>
+        <v>-15.40919581040298</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-13.1213059386434</v>
+        <v>-13.478772341618</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-14.07204087665217</v>
+        <v>-14.39251817727705</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>40</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.519083969465655</v>
+        <v>2.489888175113023</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.907897876401826</v>
+        <v>0.9067110899571702</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.6433516352351489</v>
+        <v>0.6428571428571459</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-7.394937917860553</v>
+        <v>-7.346391998094781</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.182274247491634</v>
+        <v>-2.134262568501313</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.35065710872162</v>
+        <v>2.399904671115337</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.710325047801078</v>
+        <v>-2.637067938021382</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.060243844131001</v>
+        <v>-0.960896518836428</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.764945002391201</v>
+        <v>-3.665036966372526</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.730566850035878</v>
+        <v>-3.606870229007633</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-9.150717703349287</v>
+        <v>-9.002028155571459</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-6.424982053122825</v>
+        <v>-6.252983293556163</v>
       </c>
     </row>
     <row r="26">
@@ -1615,150 +1615,150 @@
         <v>46</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-4.654829074012611</v>
+        <v>-4.684024868365242</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-6.266015167076439</v>
+        <v>-6.267201953521095</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.312960464874891</v>
+        <v>-2.313113854879212</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.165090765669987</v>
+        <v>2.164596273291984</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.800714256052494</v>
+        <v>3.849260175818266</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.423650844747208</v>
+        <v>-2.399693435797595</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.508361204013305</v>
+        <v>-2.460349525022984</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-13.9059772217142</v>
+        <v>-13.8327201119345</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-12.58198297456579</v>
+        <v>-12.48263564927122</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-12.78668413282598</v>
+        <v>-12.68677609680731</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.30289161639277</v>
+        <v>-2.154202068614943</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.077155966166167</v>
+        <v>-1.905157206599505</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 94.27</t>
+          <t>X ≈ 94.25</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>59</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.328373657652996</v>
+        <v>-3.357569452005627</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-6.634475004954112</v>
+        <v>-6.635661791398768</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.2495853727600448</v>
+        <v>-0.2497387627643661</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.814275483408977</v>
+        <v>-1.81476997578698</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.352565036504615</v>
+        <v>-2.304019116738843</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.334639501605039</v>
+        <v>1.358596910554652</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.139901366135753</v>
+        <v>-2.091889687145432</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-9.386631026871612</v>
+        <v>-9.337383464477895</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-9.447613183394367</v>
+        <v>-9.37435607361467</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-6.907701471249652</v>
+        <v>-6.808354145955079</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3327416125606959</v>
+        <v>-0.2328335765420206</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.786382302506496</v>
+        <v>4.910078923534741</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.061146703430374</v>
+        <v>6.209836251208202</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.981797607894187</v>
+        <v>8.153796367460849</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 97.99</t>
+          <t>X ≈ 97.98</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>35</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>7.519083969465647</v>
+        <v>7.489888175113016</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-8.772587794067505</v>
+        <v>-8.772741184071826</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.785219793336289</v>
+        <v>-5.785714285714292</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-6.323509346431983</v>
+        <v>-6.274963426666211</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.311849602511181</v>
+        <v>-0.2878921935615679</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.460582895365505</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.993514251578858</v>
+        <v>2.042761813972575</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.9246107620868216</v>
+        <v>-0.8513536523071252</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.774529558416724</v>
+        <v>-1.67518223312215</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.836373573819735</v>
+        <v>-4.73646553780106</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-13.37342399289302</v>
+        <v>-13.24972737186478</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-10.93643198906357</v>
+        <v>-10.78774244128574</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-7.853553481694185</v>
+        <v>-7.681554722127522</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>29</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.7567780994998685</v>
+        <v>-0.7859738938524998</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.080311669505264</v>
+        <v>1.079124883060608</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-13.10756316352568</v>
+        <v>-13.10771655353</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-6.080786295799342</v>
+        <v>-6.081280788177345</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-6.619075848895037</v>
+        <v>-6.570529929129265</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.5748499048779792</v>
+        <v>0.5988073138275922</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.95813631645715</v>
+        <v>-2.910124637466829</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.02307090182497262</v>
+        <v>0.07231846421868937</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.858640469440175</v>
+        <v>6.931897579219871</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>12.90527339724835</v>
+        <v>13.00462072254292</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>12.70057223898806</v>
+        <v>12.80048027500673</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.286674529274471</v>
+        <v>9.410371150302716</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>15.76307540009898</v>
+        <v>15.91176494787681</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>15.98881105032552</v>
+        <v>16.16080980989218</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>22</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-11.57182512144351</v>
+        <v>-11.60102091579614</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-13.18301121450727</v>
+        <v>-13.18419800095192</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-22.66869169017134</v>
+        <v>-22.66884508017566</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-22.53846654658304</v>
+        <v>-22.53896103896104</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-9.440392463315099</v>
+        <v>-9.391846543549327</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-18.23392752458917</v>
+        <v>-18.20997011563956</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-18.31863788385527</v>
+        <v>-18.27062620486495</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-14.2402519821874</v>
+        <v>-14.19100441979369</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-9.755779593255696</v>
+        <v>-9.682522483475999</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-6.060243844131072</v>
+        <v>-5.960896518836499</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.230566850035814</v>
+        <v>-6.106870229007569</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-6.424982053122818</v>
+        <v>-6.252983293556156</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>19</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-5.112494977902699</v>
+        <v>-5.14169077225533</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-11.98683896570337</v>
+        <v>-11.98802575214803</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.855294560984724</v>
+        <v>-1.855447950989046</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.725069417396504</v>
+        <v>-1.725563909774507</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-12.78967475996582</v>
+        <v>-12.74112884020005</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-17.7554586250675</v>
+        <v>-17.73150121611788</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-2.050695300123216</v>
+        <v>-2.002683621132896</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-18.30723762812048</v>
+        <v>-18.25799006572677</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-18.36821978464318</v>
+        <v>-18.29496267486348</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-13.9549806862362</v>
+        <v>-13.85563336094162</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-3.633366055022783</v>
+        <v>-3.533458019004108</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.664169992069311</v>
+        <v>1.787866613097556</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.507177033492752</v>
+        <v>6.65586658127058</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>6.732912683719427</v>
+        <v>6.904911443286089</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>19</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1506629168340652</v>
+        <v>0.1214671224814339</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>9.065792613243858</v>
+        <v>9.064605826799202</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>24.46049491269934</v>
+        <v>24.46034152269502</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>14.06440426681417</v>
+        <v>14.06390977443617</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.262956818981628</v>
+        <v>8.3115027387474</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.297172953879802</v>
+        <v>3.321130362829415</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.475620489350469</v>
+        <v>8.523632168340789</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.745393950826923</v>
+        <v>2.79464151322064</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>13.21072758377773</v>
+        <v>13.28398469355742</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.09765089271103</v>
+        <v>7.196998218005604</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.892949734450902</v>
+        <v>6.992857770469577</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.927327886806225</v>
+        <v>7.05102450783447</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.77033492822974</v>
+        <v>11.91902447600757</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>11.99607057845619</v>
+        <v>12.16806933802285</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>10</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>5.512973101642459</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>5.642857142857139</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-14.89493791786069</v>
+        <v>-14.84639199809492</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-24.59756388822547</v>
+        <v>-24.57360647927585</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-14.68227424749163</v>
+        <v>-14.63426256850131</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-15.14934289127844</v>
+        <v>-15.10009532888473</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-15.21032504780115</v>
+        <v>-15.13706793802145</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3.939756155868992</v>
+        <v>4.039103481163565</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-16.2649450023912</v>
+        <v>-16.16503696637253</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.230566850035949</v>
+        <v>-6.106870229007704</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-46.65071770334936</v>
+        <v>-46.50202815557153</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-36.42498205312275</v>
+        <v>-36.25298329355609</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-13.59202714164546</v>
+        <v>-13.62122293599809</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-20.75876879026485</v>
+        <v>-20.75995557670951</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-21.15354017501989</v>
+        <v>-21.15369356502421</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-21.02331503143153</v>
+        <v>-21.02380952380953</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-16.00604902897166</v>
+        <v>-15.95750310920589</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-21.26423055489214</v>
+        <v>-21.24027314594252</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-21.34894091415831</v>
+        <v>-21.30092923516798</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-44.03823178016727</v>
+        <v>-43.98898421777355</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-32.98810282557896</v>
+        <v>-32.91484571579927</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-28.28246606635323</v>
+        <v>-28.18311874105866</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-34.04272278016894</v>
+        <v>-33.94281474415026</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-39.56390018336913</v>
+        <v>-39.44020356234088</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-45.53960659223814</v>
+        <v>-45.39091704446031</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-50.86942649756716</v>
+        <v>-50.6974277380005</v>
       </c>
     </row>
   </sheetData>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4081</v>
+        <v>4092</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2581510085509677</v>
+        <v>-0.2567622511963634</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1219091111378816</v>
+        <v>-0.1215540172553133</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3079878778546927</v>
+        <v>-0.3071585093738776</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3356266096927527</v>
+        <v>-0.334714773281334</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3472606562468599</v>
+        <v>-0.3474892914378671</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.37892852505599</v>
+        <v>-0.3784845280563331</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.3280668110924196</v>
+        <v>-0.3283342933122384</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.3903509656605522</v>
+        <v>-0.3904808828133994</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.3400362568075082</v>
+        <v>-0.3408756021659443</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3197297682436187</v>
+        <v>-0.3212480813364351</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2904102325577043</v>
+        <v>-0.2920210933566523</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3157982975009759</v>
+        <v>-0.3179107761497875</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.3302865421537931</v>
+        <v>-0.3329590131331486</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3602920261685725</v>
+        <v>-0.3634427265961762</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3931</v>
+        <v>3942</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2243237384451007</v>
+        <v>-0.2218690941663795</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1230430315363051</v>
+        <v>-0.1226262899113237</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1743417985612297</v>
+        <v>-0.1738470349626553</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1572065987156321</v>
+        <v>-0.156737998843262</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3010292884189312</v>
+        <v>-0.3032383661028746</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2436669600711099</v>
+        <v>-0.2444925552252215</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.263787706100068</v>
+        <v>-0.2660680888862146</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.4122334170594257</v>
+        <v>-0.4141784089251814</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5101217957686259</v>
+        <v>-0.513303053298884</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5583378720852679</v>
+        <v>-0.5630252567989373</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.6218336653296888</v>
+        <v>-0.6263804391228405</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.6750112944803206</v>
+        <v>-0.6809067401638202</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.699547815251627</v>
+        <v>-0.7069482671616214</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.7139670442191672</v>
+        <v>-0.7227955715875396</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3710</v>
+        <v>3721</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.5335617463549269</v>
+        <v>-0.5283228586309576</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.6262235636841567</v>
+        <v>-0.6242291725662739</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.4691363409251039</v>
+        <v>-0.4677342938559264</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.5932075045498095</v>
+        <v>-0.5913964084695849</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.9019290445074972</v>
+        <v>-0.9053732313387499</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.7783062228139528</v>
+        <v>-0.7790234811530325</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.7947305294394482</v>
+        <v>-0.798425658630066</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.7898165188348827</v>
+        <v>-0.7936826645433612</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.8900020329962999</v>
+        <v>-0.8965955816070732</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.944465707351263</v>
+        <v>-0.9541851094404663</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.9727284658978022</v>
+        <v>-0.982437610840833</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.9773340914151945</v>
+        <v>-0.9900289719568676</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.0861798429343</v>
+        <v>-1.101705748263562</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.168917363095801</v>
+        <v>-1.187140778103256</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3491</v>
+        <v>3502</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.7115096378402939</v>
+        <v>-0.7162621665726334</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.452364755627876</v>
+        <v>-0.4333629630191993</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1750516922481324</v>
+        <v>-0.2135226248532689</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2578194587380054</v>
+        <v>-0.2961568212351935</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4949379178605469</v>
+        <v>-0.5419450197595523</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.4678125306947436</v>
+        <v>-0.49720967197824</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.5084606397157643</v>
+        <v>-0.529359489824003</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.4453108638262719</v>
+        <v>-0.4535730939929721</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.4620412949407324</v>
+        <v>-0.4749635753182844</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.495150854145308</v>
+        <v>-0.5130927538620966</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.741189993805051</v>
+        <v>-0.7584749121642531</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.7481734918910092</v>
+        <v>-0.7701122381400509</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.9806146105657803</v>
+        <v>-1.006738403930008</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.054028171713419</v>
+        <v>-1.084508136502983</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3218</v>
+        <v>3228</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4363063651068444</v>
+        <v>-0.4519255048622242</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1267985300418033</v>
+        <v>-0.1304406128292186</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2117805715502499</v>
+        <v>-0.2287425998130956</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5152605085071116</v>
+        <v>-0.5324293235411304</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3551176513591585</v>
+        <v>-0.3403529767259315</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.5368075336067406</v>
+        <v>-0.5630769035558174</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.5737471157086844</v>
+        <v>-0.592763652428232</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.5277548019483547</v>
+        <v>-0.5321176268097147</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6338435088622703</v>
+        <v>-0.6310289166526033</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.6598714046524208</v>
+        <v>-0.6496546482882763</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.8163265609133958</v>
+        <v>-0.822825755471321</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.8578960425824604</v>
+        <v>-0.8714303281402209</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.105517330562705</v>
+        <v>-1.111693583080751</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.266498522979809</v>
+        <v>-1.296353801610614</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2863</v>
+        <v>2871</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1994809904786194</v>
+        <v>-0.2286767848312508</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.5578456297978533</v>
+        <v>0.5566588433531976</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.9641888392608493</v>
+        <v>0.964035449256528</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.059582913535387</v>
+        <v>1.059088421157384</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.252745816030078</v>
+        <v>1.30129173579585</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.9231605980162598</v>
+        <v>0.9471180069658729</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.6835794110449598</v>
+        <v>0.7123065711712755</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.5146515318655744</v>
+        <v>0.5251223652985573</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3336080065921507</v>
+        <v>0.3488254789064484</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.06113739060913304</v>
+        <v>0.08229400711271495</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.01558535350551438</v>
+        <v>0.01747783683192949</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.3492404975053418</v>
+        <v>-0.3423282575691147</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.7498797145224714</v>
+        <v>-0.7374861841329405</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.133329939954741</v>
+        <v>-1.150231639080303</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2560</v>
+        <v>2567</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03174466288208322</v>
+        <v>0.002548868529451909</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.6410494151630246</v>
+        <v>0.6398626287183689</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.025397625265789</v>
+        <v>1.025244235261468</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.9997988498825947</v>
+        <v>0.9993043575045917</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.162716932158922</v>
+        <v>1.211262851924694</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.109487144108002</v>
+        <v>1.133444553057615</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.007515308237132</v>
+        <v>1.03383248408926</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.008100600537688</v>
+        <v>1.0354714806206</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.8520531198401784</v>
+        <v>0.8816309322551348</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5700213664774125</v>
+        <v>0.6031860678406176</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.7385665075580761</v>
+        <v>0.7496494379905414</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3658422053895691</v>
+        <v>0.3793003981836449</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.0712565553602218</v>
+        <v>-0.05481350812307539</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.3312320531227542</v>
+        <v>-0.3511523625081807</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2286</v>
+        <v>2291</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1893402994125779</v>
+        <v>-0.2185360937652092</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.731119177143853</v>
+        <v>0.7299323906991972</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.078381838656817</v>
+        <v>1.078228448652496</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.077659797609655</v>
+        <v>1.077165305231652</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.063158983056077</v>
+        <v>1.111704902821849</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.011340520329753</v>
+        <v>1.035297929279366</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.7520339148828796</v>
+        <v>0.8000455938732003</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.5905087019123769</v>
+        <v>0.6397562643060937</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.4858774838444191</v>
+        <v>0.5591345936241154</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1842976405851502</v>
+        <v>0.2590947513512489</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3973529443104127</v>
+        <v>0.4477958577217578</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.01943314996412226</v>
+        <v>0.0694719796348835</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.2012205455005827</v>
+        <v>-0.151089700748237</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.8256819656336845</v>
+        <v>-0.8186751311815783</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2110081967836877</v>
+        <v>0.1818124024310563</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.7932418444975298</v>
+        <v>0.792055058052874</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.046526292244984</v>
+        <v>1.046372902240662</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.725106371027763</v>
+        <v>1.72461187864976</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.685321304472446</v>
+        <v>1.733867224238217</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.334639501605039</v>
+        <v>1.358596910554652</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.9009760017606112</v>
+        <v>0.9489876807509319</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.5336082552819477</v>
+        <v>0.5828558176756644</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.9212801366455139</v>
+        <v>0.9945372464252102</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.747736205744296</v>
+        <v>0.8187644981127207</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.319885336930156</v>
+        <v>1.362380780387198</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.8837616572032658</v>
+        <v>0.9220430312117074</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.7918397392081573</v>
+        <v>0.8259877965721145</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.09675707731202721</v>
+        <v>0.1278741341607557</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1380588876772038</v>
+        <v>-0.1672546820298351</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.5364693049732452</v>
+        <v>0.5352825185285894</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.6559836345039187</v>
+        <v>0.6558302444995974</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.129065920949422</v>
+        <v>1.128571428571419</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9336335107108766</v>
+        <v>0.9821794304766485</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.8881503974888147</v>
+        <v>0.9121078064384278</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5177257525083689</v>
+        <v>0.5657374314986896</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3363713944359077</v>
+        <v>0.3856189568296244</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.903960666484565</v>
+        <v>0.9772177762642613</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.115285029511071</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.91583302964542</v>
+        <v>1.949248747913195</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.606961754083116</v>
+        <v>1.664558342420939</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.587268566673593</v>
+        <v>1.669400415857112</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.069297123078613</v>
+        <v>1.175588135015339</v>
       </c>
     </row>
     <row r="16">
@@ -2737,98 +2737,98 @@
         <v>1547</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.5093581766235502</v>
+        <v>-0.5385539709761815</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1813070363325053</v>
+        <v>-0.1824938227771611</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.134975231142576</v>
+        <v>0.1348218411382547</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5237653391782615</v>
+        <v>0.5232708468002585</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1793995094180545</v>
+        <v>0.2279454291838263</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1696388720651569</v>
+        <v>-0.1456814631155439</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.4482729546668125</v>
+        <v>-0.4002612756764918</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7860591162298931</v>
+        <v>-0.7368115538361764</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.3945525849698583</v>
+        <v>-0.321295475190162</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.5334177290695976</v>
+        <v>-0.4340704037750243</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2961409704594757</v>
+        <v>0.396049006478151</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.07195415836748253</v>
+        <v>0.1956507793957272</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1689332339487066</v>
+        <v>0.3176227817265342</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1361039197279226</v>
+        <v>0.3081026792945849</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 55.14</t>
+          <t>X &gt; 55.13</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1260</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.05876650914819237</v>
+        <v>0.02957071479556106</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.5206735521696118</v>
+        <v>-0.5218603386142675</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.280524302004018</v>
+        <v>-0.2806776920083394</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2465262384097429</v>
+        <v>0.2460317460317398</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.02569700277437192</v>
+        <v>0.07424292254014375</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.08497579431421087</v>
+        <v>0.1089332032638239</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.07909964431703287</v>
+        <v>-0.03108796532671221</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.7842635261990125</v>
+        <v>-0.7350159638052958</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.05159488907098364</v>
+        <v>0.02166222070871271</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.1078628917500524</v>
+        <v>-0.008515566455479018</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6398169023707041</v>
+        <v>0.7397249383893794</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1980045785355529</v>
+        <v>0.3217011995637975</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1746791220475359</v>
+        <v>0.3233686698253635</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.08295445481375197</v>
+        <v>0.2549532143804143</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>1030</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.05373156451493344</v>
+        <v>-0.08292735886756475</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.664917657578762</v>
+        <v>-1.666104444023418</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.477164770489139</v>
+        <v>-1.477318160493461</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.249852248260005</v>
+        <v>-1.250346740638008</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.914355393588707</v>
+        <v>-0.8658094738229352</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4228066066720686</v>
+        <v>-0.3988491977224555</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.5075169659382368</v>
+        <v>-0.4595052869479161</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.362935124288079</v>
+        <v>-1.313687561894362</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.6472182516846487</v>
+        <v>-0.5739611419049524</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.8175253975290602</v>
+        <v>-0.7181780722344868</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.2455275266630537</v>
+        <v>-0.1456194906443784</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.8907610247931643</v>
+        <v>-0.7670644037649197</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.9225623635434559</v>
+        <v>-0.7738728157656283</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.6968267133169235</v>
+        <v>-0.5248279537502611</v>
       </c>
     </row>
     <row r="19">
@@ -2893,98 +2893,98 @@
         <v>909</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4457125101823181</v>
+        <v>-0.4749083045349494</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.056898603246147</v>
+        <v>-2.058085389690802</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.791603981400527</v>
+        <v>-1.791757371404849</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.891301830111388</v>
+        <v>-0.891796322489391</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.429591383207082</v>
+        <v>-1.381045463441311</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.682272359072549</v>
+        <v>-1.658314950122936</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.326938713938276</v>
+        <v>-1.278927034947955</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.904018358825134</v>
+        <v>-1.854770796431417</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.8648905043468105</v>
+        <v>-0.7916333945671141</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.7247102907756755</v>
+        <v>-0.6253629654811022</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2807095630653507</v>
+        <v>0.3806175990840259</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.8950332966805448</v>
+        <v>-0.7713366756523001</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.205173148893834</v>
+        <v>-1.056483601116007</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.199459500867533</v>
+        <v>-1.027460741300871</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 66.32</t>
+          <t>X &gt; 66.31</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>797</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.288946143457814</v>
+        <v>-1.318141937810445</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.649191207663421</v>
+        <v>-2.650377994108077</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.040198476985594</v>
+        <v>-2.040351866989916</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.408091275680789</v>
+        <v>-1.408585768058792</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.82091031434738</v>
+        <v>-1.772364394581608</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.15088885685784</v>
+        <v>-2.126931447908227</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.608246643978461</v>
+        <v>-1.56023496498814</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.828138374339851</v>
+        <v>-2.778890811946134</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.136297444287976</v>
+        <v>-2.06304033450828</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.731511096326741</v>
+        <v>-1.632163771032168</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.8069776247249507</v>
+        <v>-0.7070695887062755</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.399952044515175</v>
+        <v>-1.27625542348693</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.318220840112154</v>
+        <v>-1.169531292334327</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.092485189885622</v>
+        <v>-0.9204864303189595</v>
       </c>
     </row>
     <row r="21">
@@ -2997,98 +2997,98 @@
         <v>703</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.9873171685144371</v>
+        <v>-1.016512962867068</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.598503261578266</v>
+        <v>-2.599690048022921</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.855294560984802</v>
+        <v>-1.855447950989124</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.156079374722182</v>
+        <v>-1.156573867100185</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.125378885143625</v>
+        <v>-1.076832965377854</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.965984940857048</v>
+        <v>-1.942027531907435</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.050695300123216</v>
+        <v>-2.002683621132896</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.371249007921328</v>
+        <v>-3.322001445527611</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.86324112176986</v>
+        <v>-2.789984011990164</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.43293232208265</v>
+        <v>-2.333584996788076</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.926395927000016</v>
+        <v>-1.82648789098134</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.029997859993202</v>
+        <v>-2.906301238964957</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.307901202638057</v>
+        <v>-3.159211654860229</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.797670531074395</v>
+        <v>-2.625671771507733</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 73.77</t>
+          <t>X &gt; 73.76</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.784631700970543</v>
+        <v>-0.8192905688483378</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.234266905504484</v>
+        <v>-2.241437058190989</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.5288767393709932</v>
+        <v>-0.5417773009340365</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.4091028468668085</v>
+        <v>0.2322291235334646</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4522884832886618</v>
+        <v>-0.5790812090448654</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.447321561892672</v>
+        <v>-1.594540456731565</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.693582809688728</v>
+        <v>-1.655196545957025</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.291507673184675</v>
+        <v>-3.40927407284601</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.7062862755879</v>
+        <v>-2.641093702916784</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.910001517798214</v>
+        <v>-2.820799900478946</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.983846456349198</v>
+        <v>-1.89772617732261</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.403426300762852</v>
+        <v>-3.288834802276554</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.854271822896948</v>
+        <v>-2.87883974977435</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.466985284140527</v>
+        <v>-2.468764291945789</v>
       </c>
     </row>
     <row r="23">
@@ -3098,49 +3098,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3313833202539769</v>
+        <v>-0.2713058547377329</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.942569413317806</v>
+        <v>-2.041050104072681</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.589677246670973</v>
+        <v>-1.501952271491874</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5966226632725267</v>
+        <v>0.6801705756929621</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.502414553374571</v>
+        <v>-0.5553472219753814</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9527040751413551</v>
+        <v>-1.02883035987287</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.411246210108459</v>
+        <v>-1.462620777456536</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-3.747473732399875</v>
+        <v>-3.607558015451815</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.126212898268435</v>
+        <v>-1.965426146976675</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.415384031046898</v>
+        <v>-2.229553235254343</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.246253413606148</v>
+        <v>-2.060559354432229</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.146454700503163</v>
+        <v>-2.935228437962856</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.632026114564233</v>
+        <v>-2.397550543631162</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.219374576487247</v>
+        <v>-1.961938517436693</v>
       </c>
     </row>
     <row r="24">
@@ -3150,101 +3150,101 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5495855584313531</v>
+        <v>-0.6899833452295923</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.375363926173286</v>
+        <v>-2.273160430385445</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.555543036250221</v>
+        <v>-2.452765656387513</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.4939874205588524</v>
+        <v>-0.39568675435914</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.67605379768888</v>
+        <v>-1.527334182248957</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.451641141444348</v>
+        <v>-2.325212474993201</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.536351500710516</v>
+        <v>-2.385868564218661</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-4.993028947728341</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-3.064402301020031</v>
+        <v>-2.888673933738801</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.626767449281218</v>
+        <v>-2.427705940677974</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.187691783507077</v>
+        <v>-2.203580863588805</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.226275004542309</v>
+        <v>-3.216077937787077</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.788056759143281</v>
+        <v>-2.754704815100375</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.34772883423863</v>
+        <v>-2.291527190772371</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 84.95</t>
+          <t>X &gt; 84.94</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>381</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.562280859930674</v>
+        <v>-1.591476654283305</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.598663803388206</v>
+        <v>-1.599850589832862</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6810992301379954</v>
+        <v>-0.6812526201423168</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.4989946798545617</v>
+        <v>0.4985001874765587</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8266964480442809</v>
+        <v>-0.7781505282785091</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.054256801611288</v>
+        <v>-1.030299392661675</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.08909839447326107</v>
+        <v>-0.04108671548294041</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.443306145871546</v>
+        <v>-3.394058583477829</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.766755493995369</v>
+        <v>-3.693498384215673</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.516936757516831</v>
+        <v>-2.417589432222258</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6219003829686258</v>
+        <v>-0.5219923469499506</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.5875222306133026</v>
+        <v>-0.4638256095850579</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.4827387007246173</v>
+        <v>-0.3340491529467897</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.2679313327040163</v>
+        <v>0.4399300922706786</v>
       </c>
     </row>
     <row r="26">
@@ -3257,150 +3257,150 @@
         <v>341</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.041033332587141</v>
+        <v>-2.070229126939772</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.892688633862115</v>
+        <v>-1.89387542030677</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.234674094863486</v>
+        <v>-0.2348274848678074</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.4820613126544941</v>
+        <v>0.4815668202764911</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.05622824044120023</v>
+        <v>-0.0076823206754284</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6386196067005443</v>
+        <v>-0.6146621977509312</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1564354299277184</v>
+        <v>0.2044471089180391</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-4.122949929401543</v>
+        <v>-4.073702367007826</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.890676953959506</v>
+        <v>-3.81741984417981</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.687809826535705</v>
+        <v>-2.588462501241132</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.2532147971126122</v>
+        <v>-0.1533067610939369</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.2188366447572889</v>
+        <v>-0.09514002372904429</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.5340330297885458</v>
+        <v>0.6827225775663734</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.053023811979891</v>
+        <v>1.225022571546553</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 92.4</t>
+          <t>X &gt; 92.39</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>295</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.633458403415709</v>
+        <v>-1.66265419776834</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.21074619139479</v>
+        <v>-1.211932977839446</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.08939767808745103</v>
+        <v>0.08924428808312967</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.2196228216758129</v>
+        <v>0.2191283292978099</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6576497822673346</v>
+        <v>-0.6091038625015628</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3602757526322478</v>
+        <v>-0.3363183436826347</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.5719630406439506</v>
+        <v>0.6199747196342713</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.962902213312269</v>
+        <v>-3.913654650918552</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.328969115597758</v>
+        <v>-2.255712005818062</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.14498960684287</v>
+        <v>-1.045642281548297</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.701156692524052</v>
+        <v>1.801064728542727</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.7185856923370082</v>
+        <v>0.8422823133652528</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.9764009407185128</v>
+        <v>1.12509048849634</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.541119641792498</v>
+        <v>1.713118401359161</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 96.13</t>
+          <t>X &gt; 96.12</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>236</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.209729589856387</v>
+        <v>-1.238925384209018</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1451860119950368</v>
+        <v>0.143999225550381</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1741434407993196</v>
+        <v>0.1739900507949983</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.7280973979470033</v>
+        <v>0.7276029055690003</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2339209687080128</v>
+        <v>-0.185375048942241</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.7840045661915696</v>
+        <v>-0.7600471572419565</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.249929142338871</v>
+        <v>1.297940821329192</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.606970009922435</v>
+        <v>-2.557722447528718</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5493080986486092</v>
+        <v>-0.4760509888689128</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2956883592588255</v>
+        <v>0.3950356845533989</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.209631268795242</v>
+        <v>2.309539304813917</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2983634602053726</v>
+        <v>-0.174666839177128</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.2947854999594526</v>
+        <v>-0.146095952181625</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.06904984973292017</v>
+        <v>0.1029489098337422</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>201</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.729672249439822</v>
+        <v>-2.758868043792454</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3607588400160893</v>
+        <v>-0.361945626460745</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.732031964283593</v>
+        <v>1.731878574279271</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.862257107871955</v>
+        <v>1.861762615493952</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.8264551169653203</v>
+        <v>0.8750010367310921</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.8662206046433738</v>
+        <v>-0.8422631956937607</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.039118787334239</v>
+        <v>1.08713046632456</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.408049358940069</v>
+        <v>-3.358801796546352</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4839568885971772</v>
+        <v>-0.4106997788174809</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.6561740663167512</v>
+        <v>0.7555213916113246</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.436547534922227</v>
+        <v>3.536455570940902</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.978388373844723</v>
+        <v>2.102084994872968</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.558237520531314</v>
+        <v>1.706927068309142</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.2864607329469</v>
+        <v>1.458459492513562</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>172</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.062311379371565</v>
+        <v>-3.091507173724196</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.6037300305749298</v>
+        <v>-0.6049168170195856</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.234056724204926</v>
+        <v>4.233903334200605</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.201491170118864</v>
+        <v>3.200996677740861</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.081806268185957</v>
+        <v>2.130352187951729</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.109191795202214</v>
+        <v>-1.085234386252601</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.713074589717671</v>
+        <v>1.761086268707992</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-3.986552193603949</v>
+        <v>-3.937304631210232</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.721952954777898</v>
+        <v>-1.648695844998201</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.40908105343334</v>
+        <v>-1.309733728138767</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.874589881329733</v>
+        <v>1.974497917348408</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.7461773360106321</v>
+        <v>0.8698739570388767</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.8367642149771939</v>
+        <v>-0.6880746671993663</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.192423913587874</v>
+        <v>-1.020425154021211</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>150</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.814249363867681</v>
+        <v>-1.843445158220312</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.241231209735155</v>
+        <v>1.240044423290499</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.179793158313451</v>
+        <v>8.17963976830913</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.97668496856847</v>
+        <v>6.976190476190467</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.771728748806112</v>
+        <v>3.820274668571884</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.402436111774541</v>
+        <v>1.426393520724154</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.651059085841702</v>
+        <v>4.699070764832022</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.482676224611708</v>
+        <v>-2.433428662217992</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.5436583811344846</v>
+        <v>-0.4704012713547883</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.7269105107976728</v>
+        <v>-0.6275631855030994</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.068388330942135</v>
+        <v>3.16829636696081</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.769433149964115</v>
+        <v>1.89312977099236</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.01594896331737772</v>
+        <v>0.1646385110952053</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4249820531227471</v>
+        <v>-0.2529832935560847</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>131</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.335877862595424</v>
+        <v>-1.365073656948056</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.15980627334838</v>
+        <v>3.158619486903724</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>9.635263896226924</v>
+        <v>9.635110506222603</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.238771482563394</v>
+        <v>8.238276990185391</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.173764372215786</v>
+        <v>6.222310291981557</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.181062065973009</v>
+        <v>4.205019474922622</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.623069263958747</v>
+        <v>5.671080942949068</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1875108302096677</v>
+        <v>-0.138263267815951</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.041583349145412</v>
+        <v>2.114840458925109</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.191664552815553</v>
+        <v>1.291011878110126</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.04039850905918</v>
+        <v>4.140306545077856</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.78470032553664</v>
+        <v>1.908396946564885</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.9255268636546248</v>
+        <v>-0.7768373158767972</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.463149992054049</v>
+        <v>-1.291151232487387</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>112</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.588058887677214</v>
+        <v>-1.617254682029845</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.157897876401819</v>
+        <v>2.156711089957163</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.120269348789641</v>
+        <v>7.12011595878532</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7.250494492378003</v>
+        <v>7.25</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.819347796425156</v>
+        <v>5.867893716190927</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.331007540345965</v>
+        <v>4.354964949295578</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.139154323936935</v>
+        <v>5.187166002927256</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.6850571769926646</v>
+        <v>-0.6358096145989478</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.1468178093417123</v>
+        <v>0.2200749191214086</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1897561558689915</v>
+        <v>0.2891034811635649</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>3.556483569037368</v>
+        <v>3.656391605056044</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.079289131920717</v>
+        <v>-2.93059958414289</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.746410624551324</v>
+        <v>-3.574411864984661</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>102</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.500523873671611</v>
+        <v>-1.529719668024242</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.770642974441031</v>
+        <v>2.769456187996376</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.277832373999722</v>
+        <v>7.277678983995401</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.408057517588084</v>
+        <v>7.407563025210081</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.850160121355131</v>
+        <v>7.898706041120903</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.167141994127476</v>
+        <v>7.191099403077089</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.082431634861308</v>
+        <v>7.130443313851629</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.7330100498980983</v>
+        <v>0.782257612291815</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.652420050238064</v>
+        <v>1.72567716001776</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1778909029545375</v>
+        <v>-0.07854357765996411</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.499760879961741</v>
+        <v>5.599668915980416</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1.612570404866091</v>
+        <v>1.736267025894335</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>1.192419551552682</v>
+        <v>1.341109099330509</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.5426291119462832</v>
+        <v>-0.3706303523796208</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>7.812659781163724</v>
+        <v>7.811472994719068</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>13.37026934878964</v>
+        <v>13.37011595878532</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>13.500494492378</v>
+        <v>13.5</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>12.96220493928231</v>
+        <v>13.01075085904808</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>13.2595789689174</v>
+        <v>13.28353637786701</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13.17486860965123</v>
+        <v>13.22288028864155</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>10.32684758491211</v>
+        <v>10.37609514730583</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9.075389237913143</v>
+        <v>9.148646347692839</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.844518060630897</v>
+        <v>5.94386538592547</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>13.97315023570403</v>
+        <v>14.0730582717227</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>11.20642515379357</v>
+        <v>11.3551147015714</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
   </sheetData>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.99527444565613</v>
+        <v>12.9660786513035</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.3840883525923</v>
+        <v>11.38290156614764</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>18.1321741106944</v>
+        <v>18.13202072069008</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>20.64335163523514</v>
+        <v>20.64285714285714</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>21.29553827261564</v>
+        <v>21.34408419238141</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>23.9738646832031</v>
+        <v>23.99782209215272</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22.69867813346075</v>
+        <v>22.74668981245107</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>24.6125618706264</v>
+        <v>24.66180943302012</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>23.36110352362742</v>
+        <v>23.43436063340712</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>22.51118472729756</v>
+        <v>22.61053205259213</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>21.11600737856118</v>
+        <v>21.21591541457985</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>22.34086172139269</v>
+        <v>22.46455834242094</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>23.11118705855549</v>
+        <v>23.25987660633331</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>23.33692270878202</v>
+        <v>23.50892146834868</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>234</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.929340379722056</v>
+        <v>3.900144585369425</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.027555996059945</v>
+        <v>4.026369209615289</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.060135038655332</v>
+        <v>4.059981648651011</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.190360182243694</v>
+        <v>4.189865689865691</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.643523620600988</v>
+        <v>6.692069540366759</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.086196795535216</v>
+        <v>6.110154204484829</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.856187290969906</v>
+        <v>6.904198969960227</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.953221211285729</v>
+        <v>9.002468773679446</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>11.02899119151509</v>
+        <v>11.10224830129479</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11.88847410458695</v>
+        <v>11.98782142988152</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.96582422837803</v>
+        <v>13.0657322643967</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>13.8549032354342</v>
+        <v>13.97859985646244</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>14.28945323682166</v>
+        <v>14.43814278459948</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>14.08783845969776</v>
+        <v>14.25983721926442</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>455</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.442160892542567</v>
+        <v>4.412965098189936</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.127678096182038</v>
+        <v>6.126491309737382</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.414225392745685</v>
+        <v>4.414072002741364</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>5.642857142857139</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.181985159062521</v>
+        <v>8.230531078828292</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.380458089796512</v>
+        <v>7.404415498746125</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.735308170090782</v>
+        <v>7.783319849081103</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.488019746084262</v>
+        <v>7.537267308477979</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.525938688462581</v>
+        <v>8.599195798242278</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.994701210814043</v>
+        <v>9.094048536108616</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.229560492114288</v>
+        <v>9.329468528132963</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.263938644469611</v>
+        <v>9.387635265497856</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.16246910983752</v>
+        <v>10.31115865761534</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>10.60798497984427</v>
+        <v>10.77998373941093</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>674</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.75053797540037</v>
+        <v>3.767583891508878</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.029559597470069</v>
+        <v>2.922959243576074</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.299476640014738</v>
+        <v>1.495247843149102</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.874805641169864</v>
+        <v>2.06826334669762</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.116931518341225</v>
+        <v>3.351540055080989</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.117569642931805</v>
+        <v>3.26663020711468</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.477963141232401</v>
+        <v>3.587959653720908</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.010894497445662</v>
+        <v>3.060142059839379</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.246648245967393</v>
+        <v>3.319905355747089</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.435305117293318</v>
+        <v>3.534652442587891</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.714283484255688</v>
+        <v>4.814191520274363</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>4.748661636611011</v>
+        <v>4.872358257639256</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.960558261042401</v>
+        <v>6.109247808820228</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.186293911268933</v>
+        <v>6.358292670835596</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.519083969465647</v>
+        <v>1.560869385968964</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.9131665803006683</v>
+        <v>0.9171495033183348</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.9983585591573316</v>
+        <v>1.045332183062087</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.137543821085195</v>
+        <v>2.173682639199882</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.599254267989501</v>
+        <v>1.534361139980533</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.31901478125711</v>
+        <v>2.389744306064465</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.55109428471534</v>
+        <v>2.598441834014409</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.295218882744855</v>
+        <v>2.297596171640002</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.762219830762731</v>
+        <v>2.741083322482751</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.862670622606053</v>
+        <v>2.819334816599948</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.397145810702781</v>
+        <v>3.413910402048529</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.537120583966235</v>
+        <v>3.577340297308147</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.384129181550399</v>
+        <v>4.404188915029174</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.8210580735932</v>
+        <v>4.928451305600021</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.4647610926485157</v>
+        <v>0.5247895408186238</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.876175630489449</v>
+        <v>-0.8662577786836891</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.919823699924095</v>
+        <v>-1.903440272217722</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.056034867832345</v>
+        <v>-2.037751222161866</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.477439836509816</v>
+        <v>-2.563286975263722</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.678977098670934</v>
+        <v>-1.717551643023</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.072443218305764</v>
+        <v>-1.128165007525709</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.7714627069465791</v>
+        <v>-0.7904080672523079</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.2948104548672035</v>
+        <v>-0.3279076326779418</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3145641435802062</v>
+        <v>0.2652302955256758</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4170826473783862</v>
+        <v>0.4098865810280898</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.219509954879641</v>
+        <v>1.199939258368033</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.105042665314301</v>
+        <v>2.073775826051815</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.868412724142985</v>
+        <v>2.904104829049267</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.02902279651821971</v>
+        <v>0.01763170162350036</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.7380648565174397</v>
+        <v>-0.7311667632198962</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.472578915438362</v>
+        <v>-1.462335540332852</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.37157373789919</v>
+        <v>-1.361466513720998</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.627980855010527</v>
+        <v>-1.694352443088597</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.484238857092215</v>
+        <v>-1.512381989479934</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.257616713245056</v>
+        <v>-1.292678410085472</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.317567190343794</v>
+        <v>-1.353965297924908</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.004717571165642</v>
+        <v>-1.047848607166429</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5462251525422204</v>
+        <v>-0.5982182795307978</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.8132316067525736</v>
+        <v>-0.8300493733204135</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.218105790845847</v>
+        <v>-0.2409484412981371</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4832386829435507</v>
+        <v>0.4544935835589783</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.8335849250703973</v>
+        <v>0.8632379618820707</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2482837574889629</v>
+        <v>0.2823012414986863</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.6456546156448368</v>
+        <v>-0.6404686675546927</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.171223640979214</v>
+        <v>-1.164242088230964</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.118856432705407</v>
+        <v>-1.111760271390885</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.097805682066607</v>
+        <v>-1.150510266310199</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.9843864174496915</v>
+        <v>-1.007837858039721</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.6152886015586176</v>
+        <v>-0.6702033718839857</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4684918274485881</v>
+        <v>-0.525796016351606</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.2874937545600673</v>
+        <v>-0.3751631761166863</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.0866427976997528</v>
+        <v>-0.005364491308647246</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.1712781583252081</v>
+        <v>-0.2328335765420206</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2888583761482622</v>
+        <v>0.2259331626192846</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5605648937768493</v>
+        <v>0.4969113990414797</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.265278723886297</v>
+        <v>1.253648006178651</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2164</v>
+        <v>2170</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1788902478455867</v>
+        <v>-0.1509730250702219</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.5223186136949138</v>
+        <v>-0.5185868018851778</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.8463205129615119</v>
+        <v>-0.8419099795129696</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.429031951671263</v>
+        <v>-1.421363040629103</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.389402862510003</v>
+        <v>-1.427392457020893</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.021191022512504</v>
+        <v>-1.038252943922316</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.5733176454602358</v>
+        <v>-0.6149699639996982</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.2763636764977662</v>
+        <v>-0.320683564178772</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5892529590765605</v>
+        <v>-0.6543093173318013</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.4225358958870089</v>
+        <v>-0.4871154700783791</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.9507121003579329</v>
+        <v>-0.9878625531189513</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.54664818090464</v>
+        <v>-0.5820083505545952</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4584811044583432</v>
+        <v>-0.4909733421214355</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.1369403128661588</v>
+        <v>0.1064637110522071</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2417</v>
+        <v>2426</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.1138121408000714</v>
+        <v>0.1344146203774628</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.198406202708199</v>
+        <v>-0.1966523226761367</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3648619667209019</v>
+        <v>-0.3631040423870928</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6659267152803139</v>
+        <v>-0.6625615763546833</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5220006241311808</v>
+        <v>-0.5548108892652124</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4498131659803164</v>
+        <v>-0.465143044600417</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1405731739986606</v>
+        <v>-0.1747475664462286</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.04814503915115864</v>
+        <v>-0.08364796046360823</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.4169366180490854</v>
+        <v>-0.4682073868079613</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.5643760755359679</v>
+        <v>-0.611102280153311</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.140978060242439</v>
+        <v>-1.162978506100806</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.9184544068775438</v>
+        <v>-0.9586000477885293</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.9021651806032125</v>
+        <v>-0.9602069771619028</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.5706171379386475</v>
+        <v>-0.6470475969361473</v>
       </c>
     </row>
     <row r="16">
@@ -4428,101 +4428,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2618</v>
+        <v>2629</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3126985646765945</v>
+        <v>0.3286466913885704</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2805214505463027</v>
+        <v>0.2800545204759004</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.02054376057031959</v>
+        <v>0.02054885921821636</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1709558229079349</v>
+        <v>-0.1699507389162562</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.03463954692818305</v>
+        <v>0.005768729729325628</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2767696989794075</v>
+        <v>0.2614333386991206</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.4796305144131239</v>
+        <v>0.4491972190555984</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6433400355508994</v>
+        <v>0.6114796236770133</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4511312998923316</v>
+        <v>0.4058325934895564</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5377729369521305</v>
+        <v>0.4766272183454916</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.04943882057713012</v>
+        <v>-0.01002176880413685</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1816468904221367</v>
+        <v>0.1074969317677343</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1266782493043976</v>
+        <v>0.03789579880116634</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1067215374043613</v>
+        <v>0.004148695793467994</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 55.14</t>
+          <t>X &lt; 55.13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2905</v>
+        <v>2916</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.01347257611351438</v>
+        <v>-0.0007229549655178857</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3816723021817268</v>
+        <v>0.380754805804159</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2113432269005457</v>
+        <v>0.2106157391552728</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.01727959406876778</v>
+        <v>0.01742993848257157</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1153572091126804</v>
+        <v>0.09377894207616322</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1226558165462421</v>
+        <v>0.1117560378240157</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2284400382226579</v>
+        <v>0.2066542977320083</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5016361537233394</v>
+        <v>0.4782756498970002</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2192282168036641</v>
+        <v>0.1864514046694126</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2477657811697824</v>
+        <v>0.2034870428074029</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.07512381944759738</v>
+        <v>-0.1184456679826695</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1161823759703111</v>
+        <v>0.06173840704445155</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1283600667814753</v>
+        <v>0.06293584854235945</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1326771551388575</v>
+        <v>0.05703042386503654</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3135</v>
+        <v>3146</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.02861382969437187</v>
+        <v>0.03816294561001143</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.6902302564463056</v>
+        <v>0.6882183730477323</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5671633638654754</v>
+        <v>0.5652379100048321</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.5241147512923732</v>
+        <v>0.5224515661777929</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.416766916745047</v>
+        <v>0.3992498402570419</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.2863050268238538</v>
+        <v>0.2773763996081087</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3463699281926509</v>
+        <v>0.3292642313718304</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5972346318034454</v>
+        <v>0.5788386812676265</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.3947704936001202</v>
+        <v>0.3691205735621708</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4545697907845607</v>
+        <v>0.4200558621159445</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2678784520383672</v>
+        <v>0.2338198135576164</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4796658563715184</v>
+        <v>0.4369671280444649</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4921394395078522</v>
+        <v>0.4410922765861542</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.3852252834003664</v>
+        <v>0.3268005589550285</v>
       </c>
     </row>
     <row r="19">
@@ -4584,101 +4584,101 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3256</v>
+        <v>3267</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1345627091413917</v>
+        <v>0.1423271995032565</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7120594431092826</v>
+        <v>0.7100047770568949</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5789361029109372</v>
+        <v>0.5770365549676555</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3585996450330668</v>
+        <v>0.357535202057619</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.5108813776984036</v>
+        <v>0.4954883437855671</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.61076944510787</v>
+        <v>0.6019660398081186</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5429785873229491</v>
+        <v>0.5276189220301504</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6753045642703768</v>
+        <v>0.6591469564804484</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4167832012022288</v>
+        <v>0.3947169030543378</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3814739472800284</v>
+        <v>0.3521575930559564</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.1020387349515488</v>
+        <v>0.07349514371922083</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.429961081210287</v>
+        <v>0.3935886269116082</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5184563832334561</v>
+        <v>0.4747160304750508</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.4853373571966557</v>
+        <v>0.4351097581733256</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 66.32</t>
+          <t>X &lt; 66.31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3368</v>
+        <v>3379</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3141150253662701</v>
+        <v>0.3200768543582981</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7599688823189794</v>
+        <v>0.75778746860653</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5589980512798078</v>
+        <v>0.557220889253081</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.4390887577928737</v>
+        <v>0.4377818994224967</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.5388790794743628</v>
+        <v>0.525508828351505</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6453271070352002</v>
+        <v>0.6374947902842294</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5473553821379937</v>
+        <v>0.5340776559523235</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8079777963327714</v>
+        <v>0.7935531201552237</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.67464382264059</v>
+        <v>0.6548942369194464</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5826980301275952</v>
+        <v>0.5569870164872412</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3651350925361285</v>
+        <v>0.3399896450999691</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5053381944745041</v>
+        <v>0.4740229978483228</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.487899096888178</v>
+        <v>0.4506345663220301</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4039965692050345</v>
+        <v>0.3613996599804565</v>
       </c>
     </row>
     <row r="21">
@@ -4688,101 +4688,101 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3462</v>
+        <v>3473</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2097314514800317</v>
+        <v>0.2150746352392332</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6574660974726285</v>
+        <v>0.6556350497849976</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4512203586205814</v>
+        <v>0.4498272922279938</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3380520960646365</v>
+        <v>0.3370862556908989</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3341027044385001</v>
+        <v>0.3230508508426055</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5321191088926938</v>
+        <v>0.5255029720312407</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.5786078510958603</v>
+        <v>0.5668868567860414</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8195152402095118</v>
+        <v>0.806774461284931</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.7458330139236864</v>
+        <v>0.7283719699716471</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.662202780219836</v>
+        <v>0.639621168825343</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.5604518230056215</v>
+        <v>0.5380700531901894</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.7844446973082313</v>
+        <v>0.7564391235103542</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.842785039936885</v>
+        <v>0.8094283786829948</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.7096222218628014</v>
+        <v>0.6718655403051272</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 73.77</t>
+          <t>X &lt; 73.76</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3546</v>
+        <v>3555</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1462264252116512</v>
+        <v>0.1524442289246792</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.5172289612809635</v>
+        <v>0.5184296209355779</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1659237927432144</v>
+        <v>0.1680488167293888</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.03030326628126545</v>
+        <v>0.06080945702263563</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1824179189889534</v>
+        <v>0.2041130524102712</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.3827399947233232</v>
+        <v>0.4081504671176361</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.4542301150189161</v>
+        <v>0.4471523669282149</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7065129645774775</v>
+        <v>0.7269195545750478</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.6330993396953275</v>
+        <v>0.6213590282706747</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6721505220661754</v>
+        <v>0.6561307360104252</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5116117741655728</v>
+        <v>0.4960085648247841</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.7592865885210571</v>
+        <v>0.7387862230587174</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6653240220524594</v>
+        <v>0.6689504721000858</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.5688137731603788</v>
+        <v>0.5683950468095915</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3630</v>
+        <v>3640</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.05820008255926012</v>
+        <v>0.04942827913711056</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4109181949081346</v>
+        <v>0.4247833791137907</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.305765876431181</v>
+        <v>0.2924855639815434</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.01148350336700332</v>
+        <v>-0.0009784735812132794</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1751362783472032</v>
+        <v>0.1823830087564104</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.2677467219999414</v>
+        <v>0.2783672049346819</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.3630928132727291</v>
+        <v>0.3698504010627062</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.6812401670274539</v>
+        <v>0.6596413688663034</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.4705552823226427</v>
+        <v>0.445922459783759</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5165310595563923</v>
+        <v>0.4880606710647726</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.4925556857453302</v>
+        <v>0.4641148315961772</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.6251600222108138</v>
+        <v>0.5927453668188392</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.5511550589751408</v>
+        <v>0.5152747831816313</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.4620702884750472</v>
+        <v>0.4228408822680834</v>
       </c>
     </row>
     <row r="24">
@@ -4844,101 +4844,101 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3699</v>
+        <v>3709</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.07835121084496421</v>
+        <v>0.09601391396309822</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4215060682638452</v>
+        <v>0.4081891872428329</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3918326911076946</v>
+        <v>0.3785644994919224</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.1593936950895483</v>
+        <v>0.1467560404102457</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.3100243259366451</v>
+        <v>0.2907785236911238</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4334585018473689</v>
+        <v>0.4169773248672684</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.4715303936308715</v>
+        <v>0.4518515326827526</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.7750835594638659</v>
+        <v>0.7545480089349965</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.5402149090023087</v>
+        <v>0.5172131605245909</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.488500417278658</v>
+        <v>0.462480804083043</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4341365751344668</v>
+        <v>0.435178550868855</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.5648938362651279</v>
+        <v>0.5624911291168573</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.5114444588128819</v>
+        <v>0.506058097797812</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4282215154092839</v>
+        <v>0.4199743769750484</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 84.95</t>
+          <t>X &lt; 84.94</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3784</v>
+        <v>3795</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1659104113934902</v>
+        <v>0.1684596036844468</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.2809221124397538</v>
+        <v>0.2802335485860041</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1376324205005304</v>
+        <v>0.1372505582898569</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.04503850924674424</v>
+        <v>0.04495963957198512</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.1802004950052591</v>
+        <v>0.1746384961218368</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.2283854788631459</v>
+        <v>0.2252365393936202</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.1581372534316046</v>
+        <v>0.1526916661120481</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4707098791701725</v>
+        <v>0.4642298487001923</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.5299758231410578</v>
+        <v>0.5208267988206572</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4075491864920053</v>
+        <v>0.3960395169624604</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.2177589849338517</v>
+        <v>0.2067376518475896</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2142297690872041</v>
+        <v>0.2007410430492556</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.2052928646824128</v>
+        <v>0.1892257959564603</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.1025020906404635</v>
+        <v>0.08430260894720476</v>
       </c>
     </row>
     <row r="26">
@@ -4948,153 +4948,153 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3824</v>
+        <v>3835</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.1904418011049458</v>
+        <v>0.1925908778157108</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.2874599201974348</v>
+        <v>0.2867474819509184</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.08939767808745103</v>
+        <v>0.08915614896434931</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.05128069105152377</v>
+        <v>0.05117963960616834</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.1011486983669485</v>
+        <v>0.09637595195724913</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1780102245093929</v>
+        <v>0.1752876138805348</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1337006937769658</v>
+        <v>0.1288816272300792</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.4903437927947394</v>
+        <v>0.4843878786133899</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.4961257226349929</v>
+        <v>0.4879320619785474</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3922117462556187</v>
+        <v>0.3819010847061577</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1761315588839523</v>
+        <v>0.1663856495732787</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1729877762056233</v>
+        <v>0.1610474149850702</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1074522312912336</v>
+        <v>0.0933837318112225</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.0342229677977457</v>
+        <v>0.01820314712187354</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 92.4</t>
+          <t>X &lt; 92.39</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3870</v>
+        <v>3881</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.1330422491463068</v>
+        <v>0.1349831930893899</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.2098041103018744</v>
+        <v>0.2093054901626559</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.06092345119328968</v>
+        <v>0.06076344079970397</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.07634132595678977</v>
+        <v>0.07616477585636972</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.1450208343951829</v>
+        <v>0.1407545314681968</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.1471498817590629</v>
+        <v>0.1448301368208362</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.1023530416494509</v>
+        <v>0.09824771956452594</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.423412526678284</v>
+        <v>0.4182993199447722</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.3251588231665892</v>
+        <v>0.3184132765951233</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2381557428591776</v>
+        <v>0.2295796716397547</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.02217092841179635</v>
+        <v>0.01415973805590198</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.09691248880709935</v>
+        <v>0.08679446324062212</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.07880955059026462</v>
+        <v>0.0667508243358057</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.009126474009036656</v>
+        <v>-0.004593703244317737</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 96.13</t>
+          <t>X &lt; 96.12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3929</v>
+        <v>3940</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.08123516175382406</v>
+        <v>0.08285554167005671</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1073396424510449</v>
+        <v>0.1071159482567623</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.05627369976860308</v>
+        <v>0.05612673363436471</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.0480228715895521</v>
+        <v>0.04792043399638146</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1076014422207052</v>
+        <v>0.1042284121356545</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1649456367935898</v>
+        <v>0.1629690019804784</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.0687420126709668</v>
+        <v>0.06550941021669843</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2763241989376368</v>
+        <v>0.2724338145517322</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.1785920848882228</v>
+        <v>0.1734517070989483</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.130958800160883</v>
+        <v>0.124296178932326</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0168454350452194</v>
+        <v>0.01046392127647522</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1672962891144607</v>
+        <v>0.158984666984253</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.168620719042579</v>
+        <v>0.1587178479809381</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.1288484380963837</v>
+        <v>0.1175750820784245</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3964</v>
+        <v>3975</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1466927197799492</v>
+        <v>0.1478620968783133</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.133249989077882</v>
+        <v>0.1329463545671388</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.02146470332177586</v>
+        <v>-0.02139719439367127</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.003351937990821341</v>
+        <v>-0.003316006452770637</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.05094680401208507</v>
+        <v>0.04818631515824023</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1607442688742324</v>
+        <v>0.159007128557441</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.08982346089415927</v>
+        <v>0.08698303672218799</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.291463154061681</v>
+        <v>0.2879981149736679</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1688636647208952</v>
+        <v>0.1644395996669914</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1141513171593189</v>
+        <v>0.1084676430132774</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.02597348739246286</v>
+        <v>-0.03130142087227483</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.04779926191570638</v>
+        <v>0.04097990928756445</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.07059377206055473</v>
+        <v>0.06235816233598257</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.05836809823949807</v>
+        <v>0.04890349889673473</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3993</v>
+        <v>4004</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1401523668695361</v>
+        <v>0.1411204379957667</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1401076142295352</v>
+        <v>0.1397788190408278</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1162441377238466</v>
+        <v>-0.1159185546464556</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.04738031580158264</v>
+        <v>-0.04722756068047573</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.002613306527258885</v>
+        <v>0.0003560706816969628</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.1637457843563936</v>
+        <v>0.1621861428577418</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.0677257525083661</v>
+        <v>0.06531359704343487</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2895168236503594</v>
+        <v>0.2864383369507593</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.2173888091273142</v>
+        <v>0.2133935236897031</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2069565561692102</v>
+        <v>0.2017781318621701</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.06638632894013341</v>
+        <v>0.06156647760052181</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1148649397012846</v>
+        <v>0.1088062562644581</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1845351759696925</v>
+        <v>0.1771229056020829</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.1740662814627711</v>
+        <v>0.1655981250253262</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4015</v>
+        <v>4026</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.07618426738024198</v>
+        <v>0.07716225285503242</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.06732176515275512</v>
+        <v>0.06718657286949536</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2394815560432306</v>
+        <v>-0.2388227863932144</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1703129610381566</v>
+        <v>-0.1698286846948989</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.04901346458023426</v>
+        <v>-0.05085296463752798</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.06313708120033823</v>
+        <v>0.06199094263787686</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.03284610229023599</v>
+        <v>-0.03470888637882297</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.2100204511737545</v>
+        <v>0.2074443536550277</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1628092805570631</v>
+        <v>0.1593845551564215</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1726499105343251</v>
+        <v>0.1681357392280773</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.03172000507520778</v>
+        <v>0.02756665735545027</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.08011276161460756</v>
+        <v>0.07485767565970036</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1470910615909489</v>
+        <v>0.1406338757173486</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1379071125061415</v>
+        <v>0.1305239096232498</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4034</v>
+        <v>4045</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.05182427092351816</v>
+        <v>0.05272701197846885</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.01071547402910511</v>
+        <v>0.01072883706093819</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2470712833841162</v>
+        <v>-0.2463957346494539</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1776177020546683</v>
+        <v>-0.1771181962304098</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.108887954961709</v>
+        <v>-0.1103288505861499</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.02062178035807705</v>
+        <v>-0.0214229115482425</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.04233363873142792</v>
+        <v>-0.04393680344701778</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.122934336444402</v>
+        <v>0.1208377740528874</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.07563682394928151</v>
+        <v>0.07280860518842758</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1061751751854842</v>
+        <v>0.1023289689383233</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.01447040508960384</v>
+        <v>0.01085236169071635</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.08756991904242284</v>
+        <v>0.08289997114062686</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1770394218056097</v>
+        <v>0.1712293827379838</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1689693598668285</v>
+        <v>0.1623442713388457</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4053</v>
+        <v>4064</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.05228613375487612</v>
+        <v>0.05304736078876005</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.05303932781633591</v>
+        <v>0.05293287602193431</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1315585477233014</v>
+        <v>-0.1311986774986451</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1110170578487839</v>
+        <v>-0.1107020127638734</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.06972866133667566</v>
+        <v>-0.07104213313038343</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.00509897810480453</v>
+        <v>-0.005826518568575523</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.00247129182660899</v>
+        <v>-0.003950605838575427</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.1352099542500866</v>
+        <v>0.1333199045305733</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.1371367560431054</v>
+        <v>0.134497557186215</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1389180981909064</v>
+        <v>0.135465329737805</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.0466920784766458</v>
+        <v>0.04347053301277271</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.119618106807529</v>
+        <v>0.1154613007513419</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2313740578741985</v>
+        <v>0.2261391261013586</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2244134563763822</v>
+        <v>0.2184733993573005</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4063</v>
+        <v>4074</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.04607121186015206</v>
+        <v>0.04677586779713039</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.04286720155518964</v>
+        <v>0.04278549034874146</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1177031598014295</v>
+        <v>-0.1173818555178912</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.09688897365265348</v>
+        <v>-0.09661396390094268</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1061363461513167</v>
+        <v>-0.1072296174922798</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.06550788233010962</v>
+        <v>-0.06601216276434485</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.03853960375698762</v>
+        <v>-0.03980042686936258</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.09764654101457637</v>
+        <v>0.09598310248789943</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.09940946547318674</v>
+        <v>0.09705807325582327</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.14826365525429</v>
+        <v>0.1450377626741073</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.006574918907375604</v>
+        <v>0.003714566617418313</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1039964955975847</v>
+        <v>0.1001955217283879</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1160145801152836</v>
+        <v>0.1114687769438802</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1342106616200454</v>
+        <v>0.1289509234296702</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4081</v>
+        <v>4092</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01389111602531301</v>
+        <v>-0.01315689187845948</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.04861324013861434</v>
+        <v>-0.0484546020506329</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2102361671997528</v>
+        <v>-0.2096688676483112</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1889632022129106</v>
+        <v>-0.1884446611409061</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1761115119925805</v>
+        <v>-0.1767992158465503</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1588258104558449</v>
+        <v>-0.1589723329343826</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1323720948497495</v>
+        <v>-0.1331647397625915</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.0967370679360684</v>
+        <v>-0.09765511414575201</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.04635050056668888</v>
+        <v>-0.04797836028163971</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.02298749001832334</v>
+        <v>0.02054879366356488</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1434954431355706</v>
+        <v>-0.1455009468365063</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.07088034501505547</v>
+        <v>-0.07365088362414696</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.08530859016947545</v>
+        <v>-0.08863944313559813</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.09075024719282965</v>
+        <v>-0.09462552229509669</v>
       </c>
     </row>
   </sheetData>
